--- a/diagrams/api-spec-v2.xlsx
+++ b/diagrams/api-spec-v2.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="应用接入配置" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IAM系统接口'!$A$1:$I$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IAM系统接口'!$A$1:$I$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -44,7 +44,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -106,6 +106,16 @@
         <fgColor rgb="00E4DFEC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5E8D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DAE8FC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -133,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -172,6 +182,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -540,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2448,8 +2464,462 @@
       </c>
       <c r="I42" s="5" t="inlineStr"/>
     </row>
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>IdP管理</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>导入SAML元数据</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/idp/saml/import</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>上传SAML元数据XML，解析IdP配置</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>multipart/form-data file (XML)</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>SAMLMetadataImportResponse</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>返回解析出的config字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>IdP管理</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>创建IdP实例</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/idp/saml/instances</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>创建SAML IdP实例（每realm仅一个）</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>{"displayName","enabled","trustEmail","config":{}}</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>IDPInstanceResponse (201)</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>alias固定为da-saml-idp</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>IdP管理</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>修改IdP实例</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/idp/saml/instances</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>修改SAML IdP配置</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>{"displayName","enabled","trustEmail","config":{}}</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>IDPInstanceResponse</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>IdP管理</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>IdP实例列表</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/idp/saml/instances</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>列出realm下所有IdP实例</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>List[IDPInstanceResponse]</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>IdP管理</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>删除IdP实例</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/idp/saml/instances/{alias}</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>删除指定IdP实例</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>IdP管理</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Mapper列表</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/idp/saml/instances/{alias}/mappers</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>获取IdP的属性映射列表</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>List[IdPMapperResponse]</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>简化返回</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>IdP管理</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>创建Mapper</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/idp/saml/instances/{alias}/mappers</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>创建属性映射</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>{"name","attributeKey","attributeValue","friendlyName"}</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>IdPMapperResponse (201)</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>固定saml-user-attribute-idp-mapper</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>IdP管理</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>修改Mapper</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/idp/saml/instances/{alias}/mappers/{mapper_id}</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>修改属性映射</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>{"name","attributeKey","attributeValue","friendlyName"}</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>部分更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>IdP管理</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>删除Mapper</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/idp/saml/instances/{alias}/mappers/{mapper_id}</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>删除属性映射</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>Token</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>授权码换Token</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/token/exchange</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>OIDC授权码换取access_token</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>{"code","redirect_uri","client_id","client_secret"}</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>TokenExchangeResponse</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>client_secret可选</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I42"/>
+  <autoFilter ref="A1:I52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2460,7 +2930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2474,7 +2944,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>已注册应用</t>
         </is>
@@ -2693,9 +3163,9 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>路径规则 (path_rules) — 32条</t>
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>路径规则 (path_rules) — 34条</t>
         </is>
       </c>
     </row>
@@ -3335,37 +3805,37 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>rubik</t>
+          <t>knowledgebase</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/knowledge/special</t>
+          <t>/kb/knowledge_bases/</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>添加特殊知识</t>
+          <t>知识库资源操作（兜底）</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>rubik-admins</t>
+          <t>kb-admins</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>仅rubik-admins可调</t>
+          <t>startswith兜底：捕获所有/{kb_id}/...子路径</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -3374,12 +3844,12 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/models/</t>
+          <t>/rubik/api/databases/knowledge/special</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>更新模型预设</t>
+          <t>添加特殊知识</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -3387,11 +3857,15 @@
           <t>rubik-admins</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>仅rubik-admins可调</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -3400,12 +3874,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/database-providers/</t>
+          <t>/rubik/api/config/models/</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>更新数据库提供者</t>
+          <t>更新模型预设</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -3417,7 +3891,7 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -3426,12 +3900,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/language</t>
+          <t>/rubik/api/config/database-providers/</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>设置语言</t>
+          <t>更新数据库提供者</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -3443,7 +3917,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
@@ -3452,12 +3926,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/languages</t>
+          <t>/rubik/api/config/language</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>分别设置语言</t>
+          <t>设置语言</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -3469,7 +3943,7 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -3478,12 +3952,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/app/</t>
+          <t>/rubik/api/config/languages</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>设置应用配置</t>
+          <t>分别设置语言</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -3495,7 +3969,7 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
@@ -3504,12 +3978,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/reload</t>
+          <t>/rubik/api/config/app/</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>重载配置</t>
+          <t>设置应用配置</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3521,7 +3995,7 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
@@ -3530,12 +4004,12 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/setup</t>
+          <t>/rubik/api/config/reload</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>初始化配置</t>
+          <t>重载配置</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -3547,29 +4021,85 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>/rubik/api/config/setup</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>初始化配置</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>rubik-admins</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>rubik</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>/rubik/api/config/llm-providers</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>LLM提供者管理</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>rubik-admins</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr"/>
+      <c r="F43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>/rubik/api/databases/</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>数据库资源操作（兜底）</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>rubik-admins</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>startswith兜底：捕获所有/{db_id}/...子路径</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/diagrams/api-spec-v2.xlsx
+++ b/diagrams/api-spec-v2.xlsx
@@ -2930,7 +2930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3120,90 +3120,78 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>httpbin</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>HTTPBin Echo</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>/anything/</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>path</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>默认RESTful</t>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>路径规则 (path_rules) — 34条</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>路径规则 (path_rules) — 34条</t>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>路径前缀</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>绑定的组</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>鉴权效果</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>应用</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>路径前缀</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>绑定的组</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>鉴权效果</t>
+      <c r="A10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>knowledgebase</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>/kb/knowledge_bases/add</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>知识库创建</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>kb-admins</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>仅kb-admins可调</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -3212,12 +3200,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/add</t>
+          <t>/kb/knowledge_bases/modify</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>知识库创建</t>
+          <t>知识库修改</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -3225,15 +3213,11 @@
           <t>kb-admins</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>仅kb-admins可调</t>
-        </is>
-      </c>
+      <c r="F11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -3242,12 +3226,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/modify</t>
+          <t>/kb/knowledge_bases/remove</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>知识库修改</t>
+          <t>知识库删除</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -3259,7 +3243,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -3268,12 +3252,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/remove</t>
+          <t>/kb/knowledge_bases/mappings/add</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>知识库删除</t>
+          <t>目录映射创建</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -3285,7 +3269,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -3294,12 +3278,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/mappings/add</t>
+          <t>/kb/knowledge_bases/mappings/remove</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>目录映射创建</t>
+          <t>目录映射删除</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -3311,7 +3295,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -3320,12 +3304,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/mappings/remove</t>
+          <t>/kb/knowledge_bases/files/upload</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>目录映射删除</t>
+          <t>文件上传</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -3337,7 +3321,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -3346,12 +3330,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/files/upload</t>
+          <t>/kb/knowledge_bases/files/remove</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>文件上传</t>
+          <t>文件删除</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -3363,7 +3347,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -3372,12 +3356,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/files/remove</t>
+          <t>/kb/knowledge_bases/files/filesystem/add</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>文件删除</t>
+          <t>文件系统创建</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -3389,7 +3373,7 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -3398,12 +3382,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/files/filesystem/add</t>
+          <t>/kb/knowledge_bases/files/filesystem/remove</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>文件系统创建</t>
+          <t>文件系统删除</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -3415,7 +3399,7 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -3424,12 +3408,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/files/filesystem/remove</t>
+          <t>/kb/models/config/add</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>文件系统删除</t>
+          <t>模型配置新增</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -3441,7 +3425,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -3450,12 +3434,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>/kb/models/config/add</t>
+          <t>/kb/models/config/modify</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>模型配置新增</t>
+          <t>模型配置修改</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -3467,7 +3451,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -3476,12 +3460,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>/kb/models/config/modify</t>
+          <t>/kb/models/config/remove</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>模型配置修改</t>
+          <t>模型配置删除</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -3493,7 +3477,7 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -3502,12 +3486,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>/kb/models/config/remove</t>
+          <t>/kb/models/config/set</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>模型配置删除</t>
+          <t>模型配置启用</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -3519,7 +3503,7 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -3528,12 +3512,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>/kb/models/config/set</t>
+          <t>/kb/prompts/add</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>模型配置启用</t>
+          <t>提示词创建</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -3545,7 +3529,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -3554,12 +3538,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>/kb/prompts/add</t>
+          <t>/kb/prompts/modify</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>提示词创建</t>
+          <t>提示词修改</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -3571,7 +3555,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -3580,12 +3564,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>/kb/prompts/modify</t>
+          <t>/kb/prompts/remove</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>提示词修改</t>
+          <t>提示词删除</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -3597,7 +3581,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -3606,12 +3590,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>/kb/prompts/remove</t>
+          <t>/kb/jargon_groups/add</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>提示词删除</t>
+          <t>黑话库创建</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -3623,7 +3607,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -3632,12 +3616,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>/kb/jargon_groups/add</t>
+          <t>/kb/jargon_groups/remove</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>黑话库创建</t>
+          <t>黑话库删除</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -3649,7 +3633,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -3658,12 +3642,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>/kb/jargon_groups/remove</t>
+          <t>/kb/jargon_groups/knowledge_bases/add</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>黑话库删除</t>
+          <t>黑话库绑定知识库</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -3675,7 +3659,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
@@ -3684,12 +3668,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>/kb/jargon_groups/knowledge_bases/add</t>
+          <t>/kb/jargon_groups/knowledge_bases/remove</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>黑话库绑定知识库</t>
+          <t>黑话库解绑知识库</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3701,7 +3685,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -3710,12 +3694,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>/kb/jargon_groups/knowledge_bases/remove</t>
+          <t>/kb/jargons/add</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>黑话库解绑知识库</t>
+          <t>黑话创建</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -3727,7 +3711,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -3736,12 +3720,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>/kb/jargons/add</t>
+          <t>/kb/jargons/modify</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>黑话创建</t>
+          <t>黑话修改</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -3753,7 +3737,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
@@ -3762,12 +3746,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>/kb/jargons/modify</t>
+          <t>/kb/jargons/remove</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>黑话修改</t>
+          <t>黑话删除</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -3779,7 +3763,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -3788,12 +3772,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>/kb/jargons/remove</t>
+          <t>/kb/knowledge_bases/</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>黑话删除</t>
+          <t>知识库资源操作（兜底）</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -3801,41 +3785,45 @@
           <t>kb-admins</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>startswith兜底：捕获所有/{kb_id}/...子路径</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>knowledgebase</t>
+          <t>rubik</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/</t>
+          <t>/rubik/api/databases/knowledge/special</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>知识库资源操作（兜底）</t>
+          <t>添加特殊知识</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>kb-admins</t>
+          <t>rubik-admins</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>startswith兜底：捕获所有/{kb_id}/...子路径</t>
+          <t>仅rubik-admins可调</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -3844,12 +3832,12 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/knowledge/special</t>
+          <t>/rubik/api/config/models/</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>添加特殊知识</t>
+          <t>更新模型预设</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -3857,15 +3845,11 @@
           <t>rubik-admins</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>仅rubik-admins可调</t>
-        </is>
-      </c>
+      <c r="F35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -3874,12 +3858,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/models/</t>
+          <t>/rubik/api/config/database-providers/</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>更新模型预设</t>
+          <t>更新数据库提供者</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -3891,7 +3875,7 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -3900,12 +3884,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/database-providers/</t>
+          <t>/rubik/api/config/language</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>更新数据库提供者</t>
+          <t>设置语言</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -3917,7 +3901,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
@@ -3926,12 +3910,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/language</t>
+          <t>/rubik/api/config/languages</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>设置语言</t>
+          <t>分别设置语言</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -3943,7 +3927,7 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -3952,12 +3936,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/languages</t>
+          <t>/rubik/api/config/app/</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>分别设置语言</t>
+          <t>设置应用配置</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -3969,7 +3953,7 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
@@ -3978,12 +3962,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/app/</t>
+          <t>/rubik/api/config/reload</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>设置应用配置</t>
+          <t>重载配置</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -3995,7 +3979,7 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
@@ -4004,12 +3988,12 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/reload</t>
+          <t>/rubik/api/config/setup</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>重载配置</t>
+          <t>初始化配置</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -4021,7 +4005,7 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
@@ -4030,12 +4014,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/setup</t>
+          <t>/rubik/api/config/llm-providers</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>初始化配置</t>
+          <t>LLM提供者管理</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -4047,7 +4031,7 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
@@ -4056,12 +4040,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/llm-providers</t>
+          <t>/rubik/api/databases/</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>LLM提供者管理</t>
+          <t>数据库资源操作（兜底）</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -4069,33 +4053,7 @@
           <t>rubik-admins</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>rubik</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>/rubik/api/databases/</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>数据库资源操作（兜底）</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>rubik-admins</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>startswith兜底：捕获所有/{db_id}/...子路径</t>
         </is>

--- a/diagrams/api-spec-v2.xlsx
+++ b/diagrams/api-spec-v2.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="应用接入配置" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IAM系统接口'!$A$1:$I$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'IAM系统接口'!$A$1:$I$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>获取IdP的属性映射列表</t>
+          <t>获取IdP的属性映射列表（saml-user-attribute-idp-mapper）</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>简化返回</t>
+          <t>仅返回属性映射类型</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>创建属性映射</t>
+          <t>创建属性映射：SAML属性→Keycloak属性</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -2872,54 +2872,238 @@
       <c r="I51" s="5" t="inlineStr"/>
     </row>
     <row r="52" ht="60" customHeight="1">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>IdP管理</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>GroupMapper列表</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/idp/saml/instances/{alias}/group-mappers</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>获取条件化自动加组规则列表（saml-advanced-group-idp-mapper）</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>List[IdPGroupMapperResponse]</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>每条规则：属性条件(AND)+目标组</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>IdP管理</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>创建GroupMapper</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/idp/saml/instances/{alias}/group-mappers</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>创建条件化自动加组规则：SAML属性命中时自动加入指定组</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>{"name","conditions":[{"attribute","value"}],"group":"/xxx-admins","regex":false}</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>IdPGroupMapperResponse (201)</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>多条件AND，group必须/开头</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>IdP管理</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>修改GroupMapper</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/idp/saml/instances/{alias}/group-mappers/{mapper_id}</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>修改条件化加组规则</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>{"name","conditions","group","regex"} 全可选</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>部分更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>IdP管理</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>删除GroupMapper</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/idp/saml/instances/{alias}/group-mappers/{mapper_id}</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>删除条件化加组规则</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>Token</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>授权码换Token</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>/api/v1/{realm}/token/exchange</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>前端</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>OIDC授权码换取access_token</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>{"code","redirect_uri","client_id","client_secret"}</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>TokenExchangeResponse</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>client_secret可选</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I52"/>
+  <autoFilter ref="A1:I56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/diagrams/api-spec-v2.xlsx
+++ b/diagrams/api-spec-v2.xlsx
@@ -1823,7 +1823,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>所有路径规则（pep-proxy提供）</t>
+          <t>所有路径规则，每条含绑定的 groups 列表</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>List[PathRuleResponse]</t>
+          <t>List[PathRuleResponse] (含required_groups:[])</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr"/>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>新建路径规则</t>
+          <t>新建路径规则，支持多组 OR 语义</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>{"path_prefix","required_group","description"}</t>
+          <t>{"path_prefix","method?","required_groups":["g1","g2"],"description"}</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>通常由init脚本预置</t>
+          <t>required_groups 至少 1 个；method 可为 null</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>单条规则</t>
+          <t>单条规则+绑定的 groups</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>修改路径规则</t>
+          <t>修改路径规则；传入 required_groups 时全量替换</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>{"path_prefix","required_group","description"}</t>
+          <t>{"path_prefix?","method?","required_groups?":["g1","g2"],"description?"}</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -1969,7 +1969,11 @@
           <t>PathRuleResponse</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>所有字段可选；required_groups 若传则 ≥1</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="60" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
@@ -1999,7 +2003,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>删除路径规则</t>
+          <t>删除路径规则（级联删除 path_rule_groups）</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">

--- a/diagrams/api-spec-v2.xlsx
+++ b/diagrams/api-spec-v2.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. IAM系统接口'!$A$1:$I$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. 权限点总表'!$A$1:$G$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. 权限点总表'!$A$1:$G$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. 业务接口权限矩阵'!$A$1:$J$138</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2948,7 +2948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Memory 全应用访问</t>
+          <t>Memory 全应用访问 — admins 专属（含 POST /tenants 与 /system/recovery 等超管动作）</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>admins, memory-admins</t>
+          <t>admins</t>
         </is>
       </c>
     </row>
@@ -4919,103 +4919,75 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>memory_health</t>
+          <t>memory_tenant_admin</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>数据面：健康检查</t>
+          <t>租户管理：/tenants/* 子路径（trailing-/ 排除 POST /tenants） + /templates* 全部 + /memory/* 数据</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/health</t>
-        </is>
-      </c>
-      <c r="F65" s="17" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>/memory/api/v1/tenants/</t>
+        </is>
+      </c>
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>ANY</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>all-users</t>
+          <t>memory-admins</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
-        <v>44</v>
-      </c>
+      <c r="A66" s="3" t="inlineStr"/>
       <c r="B66" s="7" t="inlineStr">
         <is>
           <t>memory</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>memory_data_rw</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>数据面：记忆增删改查（add/query/update/delete）</t>
-        </is>
-      </c>
+      <c r="C66" s="3" t="inlineStr"/>
+      <c r="D66" s="5" t="inlineStr"/>
       <c r="E66" s="5" t="inlineStr">
         <is>
+          <t>/memory/api/v1/templates</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr"/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr"/>
+      <c r="D67" s="5" t="inlineStr"/>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
           <t>/memory/api/v1/memory/</t>
         </is>
       </c>
-      <c r="F66" s="16" t="inlineStr">
+      <c r="F67" s="16" t="inlineStr">
         <is>
           <t>ANY</t>
         </is>
       </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>memory_system</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>数据面：系统级（故障恢复）</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>/memory/api/v1/system/</t>
-        </is>
-      </c>
-      <c r="F67" s="16" t="inlineStr">
-        <is>
-          <t>ANY</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+      <c r="G67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
@@ -5024,17 +4996,17 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>memory_tenant_manage</t>
+          <t>memory_user_data</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>管理面：租户/实例/用户记忆管理</t>
+          <t>数据面：记忆增删改查（add/query/update/delete）</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/tenants</t>
+          <t>/memory/api/v1/memory/</t>
         </is>
       </c>
       <c r="F68" s="16" t="inlineStr">
@@ -5044,13 +5016,13 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>memory-admins</t>
+          <t>all-users</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
@@ -5059,12 +5031,12 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>memory_template_manage</t>
+          <t>memory_user_templates_read</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>管理面：模板管理</t>
+          <t>数据面：模板只读（末端用户查看已生效模板）</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -5072,19 +5044,54 @@
           <t>/memory/api/v1/templates</t>
         </is>
       </c>
-      <c r="F69" s="16" t="inlineStr">
-        <is>
-          <t>ANY</t>
+      <c r="F69" s="17" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>memory-admins</t>
+          <t>all-users</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>memory_health</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>数据面：健康检查</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>/memory/api/v1/health</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>all-users</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G69"/>
+  <autoFilter ref="A1:G70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5177,7 +5184,7 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>✓ 全权</t>
+          <t>✓ 全权（含 POST /tenants 与 /system/recovery）</t>
         </is>
       </c>
     </row>
@@ -5286,9 +5293,9 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>✓ 全权</t>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>租户管理：/tenants/* 子路径 + /templates* 全部 + /memory/* 数据（✗ POST /tenants、✗ /system/recovery）</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5332,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>数据面全开；管理面 ✗</t>
+          <t>数据面全开（/memory/*、/health） + /templates GET 只读；管理面写 ✗</t>
         </is>
       </c>
     </row>
@@ -11330,7 +11337,7 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>memory_system</t>
+          <t>memory_user_data</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
@@ -11340,7 +11347,7 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/system/recovery</t>
+          <t>/memory/api/v1/memory/add</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
@@ -11368,11 +11375,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J120" s="5" t="inlineStr">
-        <is>
-          <t>semantically admin; 按用户意图=all-users</t>
-        </is>
-      </c>
+      <c r="J120" s="5" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="28" t="inlineStr">
@@ -11382,7 +11385,7 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>memory_data_rw</t>
+          <t>memory_user_data</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
@@ -11392,7 +11395,7 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/memory/add</t>
+          <t>/memory/api/v1/memory/query</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -11430,7 +11433,7 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>memory_data_rw</t>
+          <t>memory_user_data</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
@@ -11440,7 +11443,7 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/memory/query</t>
+          <t>/memory/api/v1/memory/update</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -11478,7 +11481,7 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>memory_data_rw</t>
+          <t>memory_user_data</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
@@ -11488,7 +11491,7 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/memory/update</t>
+          <t>/memory/api/v1/memory/delete</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -11526,17 +11529,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>memory_data_rw</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>memory_user_templates_read</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/memory/delete</t>
+          <t>/memory/api/v1/templates</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
@@ -11564,7 +11567,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J124" s="5" t="inlineStr"/>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>all-users 只读（含子路径 GET）</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="28" t="inlineStr">
@@ -11574,17 +11581,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>memory_tenant_manage</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>memory_user_templates_read</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/tenants</t>
+          <t>/memory/api/v1/templates/{id}</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -11607,16 +11614,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I125" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="J125" s="5" t="inlineStr">
-        <is>
-          <t>管理面仅 memory-admins</t>
-        </is>
-      </c>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J125" s="5" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="28" t="inlineStr">
@@ -11626,17 +11629,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>memory_tenant_manage</t>
-        </is>
-      </c>
-      <c r="C126" s="8" t="inlineStr">
-        <is>
-          <t>DELETE</t>
+          <t>memory_user_templates_read</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/tenants/{id}</t>
+          <t>/memory/api/v1/templates/{id}/filters</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -11659,9 +11662,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I126" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="I126" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr"/>
@@ -11674,17 +11677,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>memory_tenant_manage</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>memory_tenant_admin</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/tenants/{id}/instances</t>
+          <t>/memory/api/v1/tenants/{id}</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -11712,7 +11715,11 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="J127" s="5" t="inlineStr"/>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
+          <t>trailing-/ 匹配</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="28" t="inlineStr">
@@ -11722,17 +11729,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>memory_tenant_manage</t>
-        </is>
-      </c>
-      <c r="C128" s="8" t="inlineStr">
-        <is>
-          <t>DELETE</t>
+          <t>memory_tenant_admin</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/tenants/{id}/instances/{name}</t>
+          <t>/memory/api/v1/tenants/{id}/instances</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
@@ -11770,7 +11777,7 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>memory_tenant_manage</t>
+          <t>memory_tenant_admin</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
@@ -11780,7 +11787,7 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/tenants/{id}/instances/{n}/users/{u}/memories</t>
+          <t>/memory/api/v1/tenants/{id}/instances/{name}</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -11818,17 +11825,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>memory_template_manage</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>memory_tenant_admin</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/templates</t>
+          <t>/memory/api/v1/tenants/{id}/instances/{n}/users/{u}/memories</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
@@ -11856,7 +11863,11 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="J130" s="5" t="inlineStr"/>
+      <c r="J130" s="5" t="inlineStr">
+        <is>
+          <t>OR 语义：path 级允许，业务规程再限制入口</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="28" t="inlineStr">
@@ -11866,12 +11877,12 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>memory_template_manage</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>memory_tenant_admin</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
@@ -11914,12 +11925,12 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>memory_template_manage</t>
-        </is>
-      </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>memory_tenant_admin</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
@@ -11962,12 +11973,12 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>memory_template_manage</t>
-        </is>
-      </c>
-      <c r="C133" s="7" t="inlineStr">
-        <is>
-          <t>PUT</t>
+          <t>memory_tenant_admin</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -12010,17 +12021,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>memory_template_manage</t>
-        </is>
-      </c>
-      <c r="C134" s="8" t="inlineStr">
-        <is>
-          <t>DELETE</t>
+          <t>memory_tenant_admin</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/templates/{id}</t>
+          <t>/memory/api/v1/templates/{id}/filters</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
@@ -12058,7 +12069,7 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>memory_template_manage</t>
+          <t>memory_tenant_admin</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -12068,7 +12079,7 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/templates/{id}/filters</t>
+          <t>/memory/api/v1/templates/{id}/llm-extraction</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -12106,17 +12117,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>memory_template_manage</t>
-        </is>
-      </c>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>memory_tenant_admin</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/templates/{id}/filters</t>
+          <t>/memory/api/v1/templates/batch/llm-extraction</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
@@ -12154,7 +12165,7 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>memory_template_manage</t>
+          <t>memory_admin_full</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
@@ -12164,7 +12175,7 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/templates/{id}/llm-extraction</t>
+          <t>/memory/api/v1/tenants</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -12182,9 +12193,9 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="H137" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="H137" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="I137" s="8" t="inlineStr">
@@ -12192,7 +12203,11 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="J137" s="5" t="inlineStr"/>
+      <c r="J137" s="5" t="inlineStr">
+        <is>
+          <t>创建 tenant — admins 专属（trailing-/ 排除 memory_tenant_admin）</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="28" t="inlineStr">
@@ -12202,7 +12217,7 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>memory_template_manage</t>
+          <t>memory_admin_full</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
@@ -12212,7 +12227,7 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/templates/batch/llm-extraction</t>
+          <t>/memory/api/v1/system/recovery</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
@@ -12230,9 +12245,9 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="H138" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="H138" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="I138" s="8" t="inlineStr">
@@ -12240,7 +12255,11 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="J138" s="5" t="inlineStr"/>
+      <c r="J138" s="5" t="inlineStr">
+        <is>
+          <t>系统恢复 — admins 专属</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J138"/>

--- a/diagrams/api-spec-v2.xlsx
+++ b/diagrams/api-spec-v2.xlsx
@@ -792,12 +792,12 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>创建内部用户，可选绑组 + 选择是否临时密码</t>
+          <t>创建内部用户（仅 username/password），可选绑组 + 选择是否临时密码</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>{"username","password","email","groups":[gid], "temporary_password":bool=true}</t>
+          <t>{"username","password","groups":[gid],"temporary_password":bool=true}</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>temporary_password=false 用于服务/测试账号</t>
+          <t>User Profile 仅声明 username；temporary_password=false 用于服务/测试账号</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>修改基本信息</t>
+          <t>修改启用状态（人名/邮箱字段已移除）</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>{"firstName","lastName","email","enabled"}</t>
+          <t>{"enabled":bool}</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>username,password,email,...</t>
+          <t>列：username,password,groups</t>
         </is>
       </c>
     </row>

--- a/diagrams/api-spec-v2.xlsx
+++ b/diagrams/api-spec-v2.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. 业务接口权限矩阵" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. IAM系统接口'!$A$1:$I$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. IAM系统接口'!$A$1:$I$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. 权限点总表'!$A$1:$G$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. 业务接口权限矩阵'!$A$1:$J$138</definedName>
   </definedNames>
@@ -48,7 +48,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -97,6 +97,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F2DCDB"/>
       </patternFill>
     </fill>
@@ -113,11 +128,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DAE8FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -162,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -210,6 +220,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -224,10 +240,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -238,7 +254,7 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -609,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1668,7 +1684,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>含 resource_patterns</t>
+          <t>含 resource_patterns + actions 嵌套</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1721,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>{"app_name","path_prefix","resource_patterns":[]}</t>
+          <t>{"app_name","path_prefix","resource_patterns":[{"resource_prefix","method","resource_type","id_source","id_field","id_query_param","share_to_admin_group_on_create","share_to_all_users_on_create","actions":[]}]}</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -1715,7 +1731,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>通常由 init 脚本预置</t>
+          <t>通常由 init 脚本预置；resource_patterns 按 (app,prefix,method) 唯一</t>
         </is>
       </c>
     </row>
@@ -1846,17 +1862,21 @@
           <t>204</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>级联删除 resource_patterns + resource_actions</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="70" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>API Key</t>
+          <t>资源模式</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>创建Key</t>
+          <t>新增模式</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1866,494 +1886,494 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/{realm}/api-keys</t>
+          <t>/api/v1/apps/{app_name}/resource-patterns</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>前端</t>
+          <t>内部(管理员)</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>创建API Key，明文只返回一次</t>
+          <t>给已存在的 app 新加一个 resource_pattern（可选嵌套 actions）</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>{"name","scope","expires_at"}</t>
+          <t>{"resource_prefix","method","resource_type","id_source","id_field","id_query_param","share_to_admin_group_on_create","share_to_all_users_on_create","actions":[]}</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>ApiKeyCreateResponse (201)</t>
+          <t>ResourcePatternResponse (201)</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>含明文 api_key 字段</t>
+          <t>(app,prefix,method) 冲突 → 409</t>
         </is>
       </c>
     </row>
     <row r="29" ht="70" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>API Key</t>
+          <t>资源模式</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Key列表</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>修改模式</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/{realm}/api-keys</t>
+          <t>/api/v1/apps/{app_name}/resource-patterns?resource_prefix=&amp;method=</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>前端</t>
+          <t>内部(管理员)</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>列出所有Key（只显示前缀）</t>
+          <t>按复合键更新 resource_pattern（不含 actions）</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{"resource_type","id_source","id_field","id_query_param","share_to_admin_group_on_create","share_to_all_users_on_create"}</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>List[ApiKeyResponse]</t>
+          <t>ResourcePatternResponse</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>无明文</t>
+          <t>method='' 表示 fallback 条目</t>
         </is>
       </c>
     </row>
     <row r="30" ht="70" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>API Key</t>
+          <t>资源模式</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Key详情</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
+          <t>删除模式</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/apps/{app_name}/resource-patterns?resource_prefix=&amp;method=&amp;cascade_actions=true</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>内部(管理员)</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>删单条 resource_pattern；cascade_actions=true 一并删同 (prefix,method) 的 actions</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="70" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>资源动作</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>新增动作</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/apps/{app_name}/resource-actions?resource_prefix=</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>内部(管理员)</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>新增 resource_action 行（独立于 pattern 的 id PK）</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>{"action","method","path_suffix","success_status","min_permission"}</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>ResourceActionResponse (201)</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>resource_prefix 必须对应已有 pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="70" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>资源动作</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>修改动作</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/apps/{app_name}/resource-actions/{action_id}</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>内部(管理员)</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>按 id 更新 resource_action 行</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>{"action","method","path_suffix","success_status","min_permission"}</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>ResourceActionResponse</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33" ht="70" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>资源动作</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>删除动作</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/apps/{app_name}/resource-actions/{action_id}</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>内部(管理员)</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>按 id 删除 resource_action 行</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="70" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>权限点CRUD</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>创建权限点</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/permission-groups</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>内部(管理员)</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>创建 permission_group + 嵌套 paths + bindings</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>{"app_name","name","description","paths":[{"path_prefix","method"}],"bindings":["all-users","kb-admins"]}</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>PermissionGroupResponse (201)</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>app_name='' 表示平台级；与 (app_name,name) 冲突 → 409</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="70" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>权限点CRUD</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>权限点列表</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>/api/v1/{realm}/api-keys/{key_id}</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>前端</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>单个Key详情</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/permission-groups</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>前端/内部</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>列出所有 permission_group（可按 app_name 过滤）</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>?app_name=</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>List[PermissionGroupResponse]</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>扁平列表；UI 聚合视图见 GET /permissions</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="70" customHeight="1">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>权限点CRUD</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>权限点详情</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/permission-groups/{group_id}</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>前端/内部</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>单个 permission_group 详情 + paths + bindings</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>ApiKeyResponse</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>无明文</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="70" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>API Key</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>修改Key</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>PermissionGroupResponse</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="70" customHeight="1">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>权限点CRUD</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>修改权限点</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>/api/v1/{realm}/api-keys/{key_id}</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>前端</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>修改Key信息</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>{"name","scope","enabled"}</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>ApiKeyResponse</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32" ht="70" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>API Key</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>删除Key</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>DELETE</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>/api/v1/{realm}/api-keys/{key_id}</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>前端</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>删除Key</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr"/>
-    </row>
-    <row r="33" ht="70" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>API Key</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>轮换Key</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>/api/v1/{realm}/api-keys/{key_id}/rotate</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>前端</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>轮换Key，subject_id 不变</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>ApiKeyCreateResponse</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>旧Key立即失效</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="70" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>资源ACL</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>添加权限 (分享)</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>/acl/v1/resources/{resource_id}/permissions</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>前端/应用</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>给资源添加权限（分享）；内部校验调用者是 owner</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>{"app_name","resource_type","subject_type","subject_id","permission"}</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>PermissionResponse (201)</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>resource-sync 提供；必须带 app_name + resource_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="70" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>资源ACL</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>查询权限</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>/acl/v1/resources/{resource_id}/permissions?app_name=..&amp;resource_type=..</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>前端/应用</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>查看资源的权限成员列表</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>query: app_name, resource_type</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>{"permissions":[PermissionResponse], "count"}</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36" ht="70" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>资源ACL</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>修改权限</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>/acl/v1/resources/{resource_id}/permissions/{acl_id}</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>前端/应用</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>修改权限等级；内部校验调用者是 owner</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>{"app_name","resource_type","permission":"contributor"}</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>PermissionResponse</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37" ht="70" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>资源ACL</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>删除权限</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>DELETE</t>
-        </is>
-      </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>/acl/v1/resources/{resource_id}/permissions/{acl_id}</t>
+          <t>/api/v1/permission-groups/{group_id}</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>前端/应用</t>
+          <t>内部(管理员)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>回收权限；内部校验调用者是 owner</t>
+          <t>修改 name/description/app_name；paths/bindings 置空数组=清空，设为 null=保持</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>{"app_name","name","description","paths":[],"bindings":[]}</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr"/>
+          <t>PermissionGroupResponse</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>paths/bindings 是 replace-all</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="70" customHeight="1">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>IdP管理</t>
+          <t>权限点CRUD</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>导入SAML元数据</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>删除权限点</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/{realm}/idp/saml/import</t>
+          <t>/api/v1/permission-groups/{group_id}</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>前端</t>
+          <t>内部(管理员)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>上传SAML元数据XML，解析IdP配置</t>
+          <t>删除 permission_group（级联删 paths + bindings）</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>multipart/form-data file (XML)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>SAMLMetadataImportResponse</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>返回解析出的 config 字段</t>
-        </is>
-      </c>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr"/>
     </row>
     <row r="39" ht="70" customHeight="1">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>IdP管理</t>
+          <t>权限点CRUD</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>创建IdP实例</t>
+          <t>新增路径</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -2363,74 +2383,70 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/{realm}/idp/saml/instances</t>
+          <t>/api/v1/permission-groups/{group_id}/paths</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>前端</t>
+          <t>内部(管理员)</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>创建SAML IdP实例（每realm仅一个）</t>
+          <t>单条新增 path_prefix/method（比 PUT replace-all 便宜）</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>{"displayName","enabled","trustEmail","config":{}}</t>
+          <t>{"path_prefix","method"}</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>IDPInstanceResponse (201)</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>alias固定为 da-saml-idp</t>
-        </is>
-      </c>
+          <t>PermissionGroupPathResponse (201)</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr"/>
     </row>
     <row r="40" ht="70" customHeight="1">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>IdP管理</t>
+          <t>权限点CRUD</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>修改IdP实例</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>PUT</t>
+          <t>删除路径</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/{realm}/idp/saml/instances</t>
+          <t>/api/v1/permission-groups/{group_id}/paths/{path_id}</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>前端</t>
+          <t>内部(管理员)</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>修改SAML IdP配置</t>
+          <t>按 path id 单条删除</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>{"displayName","enabled","trustEmail","config":{}}</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>IDPInstanceResponse</t>
+          <t>204</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr"/>
@@ -2438,32 +2454,32 @@
     <row r="41" ht="70" customHeight="1">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>IdP管理</t>
+          <t>权限点CRUD</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>IdP实例列表</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>新增绑定</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>/api/v1/{realm}/idp/saml/instances</t>
+          <t>/api/v1/permission-groups/{group_id}/bindings/{kc_group_name}</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>前端</t>
+          <t>内部(管理员)</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>列出 realm 下所有 IdP 实例</t>
+          <t>把该权限点开给指定 Keycloak 组（幂等）</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -2473,7 +2489,7 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>List[IDPInstanceResponse]</t>
+          <t>{"group_id","kc_group_name"}</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
@@ -2481,463 +2497,1136 @@
     <row r="42" ht="70" customHeight="1">
       <c r="A42" s="13" t="inlineStr">
         <is>
+          <t>权限点CRUD</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>删除绑定</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/permission-groups/{group_id}/bindings/{kc_group_name}</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>内部(管理员)</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>回收该权限点对指定 Keycloak 组的授权</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43" ht="70" customHeight="1">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>API Key</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>创建Key</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/api-keys</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>创建API Key，明文只返回一次</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>{"name","scope","expires_at"}</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>ApiKeyCreateResponse (201)</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>含明文 api_key 字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="70" customHeight="1">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>API Key</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Key列表</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/api-keys</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>列出所有Key（只显示前缀）</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>List[ApiKeyResponse]</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>无明文</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="70" customHeight="1">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>API Key</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Key详情</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/api-keys/{key_id}</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>单个Key详情</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>ApiKeyResponse</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>无明文</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="70" customHeight="1">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>API Key</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>修改Key</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/api-keys/{key_id}</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>修改Key信息</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>{"name","scope","enabled"}</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>ApiKeyResponse</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47" ht="70" customHeight="1">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>API Key</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>删除Key</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/api-keys/{key_id}</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>删除Key</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48" ht="70" customHeight="1">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>API Key</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>轮换Key</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/api-keys/{key_id}/rotate</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>轮换Key，subject_id 不变</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>ApiKeyCreateResponse</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>旧Key立即失效</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="70" customHeight="1">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>资源ACL</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>添加权限 (分享)</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>/acl/v1/resources/{resource_id}/permissions</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>前端/应用</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>给资源添加权限（分享）；内部校验调用者是 owner</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>{"app_name","resource_type","subject_type","subject_id","permission"}</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>PermissionResponse (201)</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>resource-sync 提供；必须带 app_name + resource_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="70" customHeight="1">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>资源ACL</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>查询权限</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>/acl/v1/resources/{resource_id}/permissions?app_name=..&amp;resource_type=..</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>前端/应用</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>查看资源的权限成员列表</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>query: app_name, resource_type</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>{"permissions":[PermissionResponse], "count"}</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51" ht="70" customHeight="1">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>资源ACL</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>修改权限</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>/acl/v1/resources/{resource_id}/permissions/{acl_id}</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>前端/应用</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>修改权限等级；内部校验调用者是 owner</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>{"app_name","resource_type","permission":"contributor"}</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>PermissionResponse</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52" ht="70" customHeight="1">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>资源ACL</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>删除权限</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>/acl/v1/resources/{resource_id}/permissions/{acl_id}</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>前端/应用</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>回收权限；内部校验调用者是 owner</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53" ht="70" customHeight="1">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
           <t>IdP管理</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>导入SAML元数据</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/idp/saml/import</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>上传SAML元数据XML，解析IdP配置</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>multipart/form-data file (XML)</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>SAMLMetadataImportResponse</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>返回解析出的 config 字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="70" customHeight="1">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>IdP管理</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>创建IdP实例</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/idp/saml/instances</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>创建SAML IdP实例（每realm仅一个）</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>{"displayName","enabled","trustEmail","config":{}}</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>IDPInstanceResponse (201)</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>alias固定为 da-saml-idp</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="70" customHeight="1">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>IdP管理</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>修改IdP实例</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/idp/saml/instances</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>修改SAML IdP配置</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>{"displayName","enabled","trustEmail","config":{}}</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>IDPInstanceResponse</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56" ht="70" customHeight="1">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>IdP管理</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>IdP实例列表</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>/api/v1/{realm}/idp/saml/instances</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>列出 realm 下所有 IdP 实例</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>List[IDPInstanceResponse]</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57" ht="70" customHeight="1">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>IdP管理</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>删除IdP实例</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>/api/v1/{realm}/idp/saml/instances/{alias}</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>前端</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>删除指定IdP实例</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr"/>
-    </row>
-    <row r="43" ht="70" customHeight="1">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="I57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58" ht="70" customHeight="1">
+      <c r="A58" s="16" t="inlineStr">
         <is>
           <t>IdP管理</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Mapper列表</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>/api/v1/{realm}/idp/saml/instances/{alias}/mappers</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>前端</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>获取 IdP 的属性映射列表（saml-user-attribute-idp-mapper）</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H58" s="5" t="inlineStr">
         <is>
           <t>List[IdPMapperResponse]</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>仅返回属性映射类型</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="70" customHeight="1">
-      <c r="A44" s="13" t="inlineStr">
+    <row r="59" ht="70" customHeight="1">
+      <c r="A59" s="16" t="inlineStr">
         <is>
           <t>IdP管理</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>创建Mapper</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>/api/v1/{realm}/idp/saml/instances/{alias}/mappers</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>前端</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>创建属性映射：SAML 属性→Keycloak 属性</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>{"name","attributeKey","attributeValue","friendlyName"}</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="H59" s="5" t="inlineStr">
         <is>
           <t>IdPMapperResponse (201)</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I59" s="5" t="inlineStr">
         <is>
           <t>固定 saml-user-attribute-idp-mapper</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="70" customHeight="1">
-      <c r="A45" s="13" t="inlineStr">
+    <row r="60" ht="70" customHeight="1">
+      <c r="A60" s="16" t="inlineStr">
         <is>
           <t>IdP管理</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>修改Mapper</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>/api/v1/{realm}/idp/saml/instances/{alias}/mappers/{mapper_id}</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>前端</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>修改属性映射</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>{"name","attributeKey","attributeValue","friendlyName"}</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H60" s="5" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>部分更新</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="70" customHeight="1">
-      <c r="A46" s="13" t="inlineStr">
+    <row r="61" ht="70" customHeight="1">
+      <c r="A61" s="16" t="inlineStr">
         <is>
           <t>IdP管理</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>删除Mapper</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>/api/v1/{realm}/idp/saml/instances/{alias}/mappers/{mapper_id}</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>前端</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F61" s="5" t="inlineStr">
         <is>
           <t>删除属性映射</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="H61" s="5" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr"/>
-    </row>
-    <row r="47" ht="70" customHeight="1">
-      <c r="A47" s="13" t="inlineStr">
+      <c r="I61" s="5" t="inlineStr"/>
+    </row>
+    <row r="62" ht="70" customHeight="1">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t>IdP管理</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>GroupMapper列表</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>/api/v1/{realm}/idp/saml/instances/{alias}/group-mappers</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>前端</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>获取条件化自动加组规则列表（saml-advanced-group-idp-mapper）</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H62" s="5" t="inlineStr">
         <is>
           <t>List[IdPGroupMapperResponse]</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>每条规则：属性条件(AND)+目标组</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="70" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
+    <row r="63" ht="70" customHeight="1">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>IdP管理</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>创建GroupMapper</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>/api/v1/{realm}/idp/saml/instances/{alias}/group-mappers</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>前端</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr">
         <is>
           <t>创建条件化自动加组规则：SAML 属性命中时自动加入指定组</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>{"name","conditions":[{"attribute","value"}],"group":"/xxx-admins","regex":false}</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H63" s="5" t="inlineStr">
         <is>
           <t>IdPGroupMapperResponse (201)</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I63" s="5" t="inlineStr">
         <is>
           <t>多条件AND，group必须/开头</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="70" customHeight="1">
-      <c r="A49" s="13" t="inlineStr">
+    <row r="64" ht="70" customHeight="1">
+      <c r="A64" s="16" t="inlineStr">
         <is>
           <t>IdP管理</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>修改GroupMapper</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>/api/v1/{realm}/idp/saml/instances/{alias}/group-mappers/{mapper_id}</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>前端</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>修改条件化加组规则</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>{"name","conditions","group","regex"} 全可选</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H64" s="5" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>部分更新</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="70" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
+    <row r="65" ht="70" customHeight="1">
+      <c r="A65" s="16" t="inlineStr">
         <is>
           <t>IdP管理</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>删除GroupMapper</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>/api/v1/{realm}/idp/saml/instances/{alias}/group-mappers/{mapper_id}</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>前端</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>删除条件化加组规则</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H65" s="5" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr"/>
-    </row>
-    <row r="51" ht="70" customHeight="1">
-      <c r="A51" s="14" t="inlineStr">
+      <c r="I65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66" ht="70" customHeight="1">
+      <c r="A66" s="17" t="inlineStr">
         <is>
           <t>Token</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>授权码换Token</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>/api/v1/{realm}/token/exchange</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>前端</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>OIDC 授权码换取 access_token</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>{"code","redirect_uri","client_id","client_secret"}</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="H66" s="5" t="inlineStr">
         <is>
           <t>TokenExchangeResponse</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I66" s="5" t="inlineStr">
         <is>
           <t>client_secret 可选</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I51"/>
+  <autoFilter ref="A1:I66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3001,7 +3690,7 @@
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>(平台级)</t>
         </is>
@@ -3021,7 +3710,7 @@
           <t>/api/v1/</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="18" t="inlineStr">
         <is>
           <t>ANY</t>
         </is>
@@ -3036,7 +3725,7 @@
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>(平台级)</t>
         </is>
@@ -3056,7 +3745,7 @@
           <t>/acl/v1/</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>ANY</t>
         </is>
@@ -3091,7 +3780,7 @@
           <t>/kb/</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="18" t="inlineStr">
         <is>
           <t>ANY</t>
         </is>
@@ -3126,7 +3815,7 @@
           <t>/kb/knowledge_bases</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -3161,7 +3850,7 @@
           <t>/kb/conversations</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -3196,7 +3885,7 @@
           <t>/kb/prompts</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -3231,7 +3920,7 @@
           <t>/kb/knowledge_bases/files/download</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -3266,7 +3955,7 @@
           <t>/kb/conversations/images/download</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -3301,7 +3990,7 @@
           <t>/kb/knowledge_bases/add</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -3336,7 +4025,7 @@
           <t>/kb/knowledge_bases/modify</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -3371,7 +4060,7 @@
           <t>/kb/knowledge_bases/remove</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -3406,7 +4095,7 @@
           <t>/kb/knowledge_bases/mappings/</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -3441,7 +4130,7 @@
           <t>/kb/knowledge_bases/files/upload</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -3476,7 +4165,7 @@
           <t>/kb/knowledge_bases/files/remove</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -3511,7 +4200,7 @@
           <t>/kb/conversations/start</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -3546,7 +4235,7 @@
           <t>/kb/conversations/stop</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -3581,7 +4270,7 @@
           <t>/kb/conversations/remove</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -3616,7 +4305,7 @@
           <t>/kb/conversations/images/generate</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -3651,7 +4340,7 @@
           <t>/kb/conversations/query/</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -3686,7 +4375,7 @@
           <t>/kb/retrieval/fusion_search</t>
         </is>
       </c>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -3721,7 +4410,7 @@
           <t>/kb/knowledge_bases/files/filesystem</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>ANY</t>
         </is>
@@ -3756,7 +4445,7 @@
           <t>/kb/models/config</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F23" s="18" t="inlineStr">
         <is>
           <t>ANY</t>
         </is>
@@ -3791,7 +4480,7 @@
           <t>/kb/prompts</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -3826,7 +4515,7 @@
           <t>/kb/jargon_groups</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F25" s="18" t="inlineStr">
         <is>
           <t>ANY</t>
         </is>
@@ -3861,7 +4550,7 @@
           <t>/kb/jargons</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F26" s="18" t="inlineStr">
         <is>
           <t>ANY</t>
         </is>
@@ -3896,7 +4585,7 @@
           <t>/rubik/</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F27" s="18" t="inlineStr">
         <is>
           <t>ANY</t>
         </is>
@@ -3931,7 +4620,7 @@
           <t>/rubik/api/databases</t>
         </is>
       </c>
-      <c r="F28" s="18" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -3956,7 +4645,7 @@
           <t>/rubik/api/databases/</t>
         </is>
       </c>
-      <c r="F29" s="19" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
@@ -3987,7 +4676,7 @@
           <t>/rubik/api/databases</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -4012,7 +4701,7 @@
           <t>/rubik/api/databases/</t>
         </is>
       </c>
-      <c r="F31" s="17" t="inlineStr">
+      <c r="F31" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -4033,7 +4722,7 @@
           <t>/rubik/api/databases/</t>
         </is>
       </c>
-      <c r="F32" s="18" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -4064,7 +4753,7 @@
           <t>/rubik/api/databases/config/data-dir</t>
         </is>
       </c>
-      <c r="F33" s="17" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -4099,7 +4788,7 @@
           <t>/rubik/api/databases/</t>
         </is>
       </c>
-      <c r="F34" s="18" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -4124,7 +4813,7 @@
           <t>/rubik/api/databases/</t>
         </is>
       </c>
-      <c r="F35" s="17" t="inlineStr">
+      <c r="F35" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -4155,7 +4844,7 @@
           <t>/rubik/api/databases/</t>
         </is>
       </c>
-      <c r="F36" s="20" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -4180,7 +4869,7 @@
           <t>/rubik/api/databases/</t>
         </is>
       </c>
-      <c r="F37" s="19" t="inlineStr">
+      <c r="F37" s="21" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
@@ -4201,7 +4890,7 @@
           <t>/rubik/api/databases/</t>
         </is>
       </c>
-      <c r="F38" s="18" t="inlineStr">
+      <c r="F38" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -4232,7 +4921,7 @@
           <t>/rubik/api/databases/knowledge/special</t>
         </is>
       </c>
-      <c r="F39" s="18" t="inlineStr">
+      <c r="F39" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -4267,7 +4956,7 @@
           <t>/rubik/api/databases/</t>
         </is>
       </c>
-      <c r="F40" s="17" t="inlineStr">
+      <c r="F40" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -4292,7 +4981,7 @@
           <t>/rubik/api/databases/</t>
         </is>
       </c>
-      <c r="F41" s="18" t="inlineStr">
+      <c r="F41" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -4323,7 +5012,7 @@
           <t>/rubik/api/databases/</t>
         </is>
       </c>
-      <c r="F42" s="18" t="inlineStr">
+      <c r="F42" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -4348,7 +5037,7 @@
           <t>/rubik/api/databases/</t>
         </is>
       </c>
-      <c r="F43" s="20" t="inlineStr">
+      <c r="F43" s="22" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -4379,7 +5068,7 @@
           <t>/rubik/api/metadata/</t>
         </is>
       </c>
-      <c r="F44" s="17" t="inlineStr">
+      <c r="F44" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -4404,7 +5093,7 @@
           <t>/rubik/api/metadata/</t>
         </is>
       </c>
-      <c r="F45" s="20" t="inlineStr">
+      <c r="F45" s="22" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -4435,7 +5124,7 @@
           <t>/rubik/api/query</t>
         </is>
       </c>
-      <c r="F46" s="18" t="inlineStr">
+      <c r="F46" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -4460,7 +5149,7 @@
           <t>/rubik/api/sessions</t>
         </is>
       </c>
-      <c r="F47" s="17" t="inlineStr">
+      <c r="F47" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -4481,7 +5170,7 @@
           <t>/rubik/api/sessions</t>
         </is>
       </c>
-      <c r="F48" s="18" t="inlineStr">
+      <c r="F48" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -4502,7 +5191,7 @@
           <t>/rubik/api/sessions/</t>
         </is>
       </c>
-      <c r="F49" s="17" t="inlineStr">
+      <c r="F49" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -4523,7 +5212,7 @@
           <t>/rubik/api/sessions/</t>
         </is>
       </c>
-      <c r="F50" s="18" t="inlineStr">
+      <c r="F50" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -4544,7 +5233,7 @@
           <t>/rubik/api/sessions/</t>
         </is>
       </c>
-      <c r="F51" s="19" t="inlineStr">
+      <c r="F51" s="21" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
@@ -4575,7 +5264,7 @@
           <t>/rubik/api/config</t>
         </is>
       </c>
-      <c r="F52" s="17" t="inlineStr">
+      <c r="F52" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -4600,7 +5289,7 @@
           <t>/rubik/api/config/</t>
         </is>
       </c>
-      <c r="F53" s="17" t="inlineStr">
+      <c r="F53" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -4631,7 +5320,7 @@
           <t>/rubik/api/config/</t>
         </is>
       </c>
-      <c r="F54" s="20" t="inlineStr">
+      <c r="F54" s="22" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -4656,7 +5345,7 @@
           <t>/rubik/api/config/</t>
         </is>
       </c>
-      <c r="F55" s="18" t="inlineStr">
+      <c r="F55" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -4677,7 +5366,7 @@
           <t>/rubik/api/config/</t>
         </is>
       </c>
-      <c r="F56" s="19" t="inlineStr">
+      <c r="F56" s="21" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
@@ -4708,7 +5397,7 @@
           <t>/rubik/api/dashboards</t>
         </is>
       </c>
-      <c r="F57" s="17" t="inlineStr">
+      <c r="F57" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -4733,7 +5422,7 @@
           <t>/rubik/api/dashboards/</t>
         </is>
       </c>
-      <c r="F58" s="17" t="inlineStr">
+      <c r="F58" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -4764,7 +5453,7 @@
           <t>/rubik/api/dashboards</t>
         </is>
       </c>
-      <c r="F59" s="18" t="inlineStr">
+      <c r="F59" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -4789,7 +5478,7 @@
           <t>/rubik/api/dashboards/</t>
         </is>
       </c>
-      <c r="F60" s="20" t="inlineStr">
+      <c r="F60" s="22" t="inlineStr">
         <is>
           <t>PUT</t>
         </is>
@@ -4810,7 +5499,7 @@
           <t>/rubik/api/dashboards/</t>
         </is>
       </c>
-      <c r="F61" s="19" t="inlineStr">
+      <c r="F61" s="21" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
@@ -4841,7 +5530,7 @@
           <t>/rubik/api/refresh/</t>
         </is>
       </c>
-      <c r="F62" s="17" t="inlineStr">
+      <c r="F62" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -4866,7 +5555,7 @@
           <t>/rubik/api/refresh/</t>
         </is>
       </c>
-      <c r="F63" s="18" t="inlineStr">
+      <c r="F63" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
@@ -4897,7 +5586,7 @@
           <t>/memory/</t>
         </is>
       </c>
-      <c r="F64" s="16" t="inlineStr">
+      <c r="F64" s="18" t="inlineStr">
         <is>
           <t>ANY</t>
         </is>
@@ -4932,7 +5621,7 @@
           <t>/memory/api/v1/tenants/</t>
         </is>
       </c>
-      <c r="F65" s="16" t="inlineStr">
+      <c r="F65" s="18" t="inlineStr">
         <is>
           <t>ANY</t>
         </is>
@@ -4957,7 +5646,7 @@
           <t>/memory/api/v1/templates</t>
         </is>
       </c>
-      <c r="F66" s="16" t="inlineStr">
+      <c r="F66" s="18" t="inlineStr">
         <is>
           <t>ANY</t>
         </is>
@@ -4978,7 +5667,7 @@
           <t>/memory/api/v1/memory/</t>
         </is>
       </c>
-      <c r="F67" s="16" t="inlineStr">
+      <c r="F67" s="18" t="inlineStr">
         <is>
           <t>ANY</t>
         </is>
@@ -5009,7 +5698,7 @@
           <t>/memory/api/v1/memory/</t>
         </is>
       </c>
-      <c r="F68" s="16" t="inlineStr">
+      <c r="F68" s="18" t="inlineStr">
         <is>
           <t>ANY</t>
         </is>
@@ -5044,7 +5733,7 @@
           <t>/memory/api/v1/templates</t>
         </is>
       </c>
-      <c r="F69" s="17" t="inlineStr">
+      <c r="F69" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -5079,7 +5768,7 @@
           <t>/memory/api/v1/health</t>
         </is>
       </c>
-      <c r="F70" s="17" t="inlineStr">
+      <c r="F70" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
@@ -5152,7 +5841,7 @@
       </c>
     </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>admins</t>
         </is>
@@ -5189,7 +5878,7 @@
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>kb-admins</t>
         </is>
@@ -5204,7 +5893,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>⚡ owner</t>
         </is>
@@ -5226,7 +5915,7 @@
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>rubik-admins</t>
         </is>
@@ -5241,7 +5930,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>⚡ owner</t>
         </is>
@@ -5263,7 +5952,7 @@
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>memory-admins</t>
         </is>
@@ -5278,7 +5967,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>⚡ owner</t>
         </is>
@@ -5300,7 +5989,7 @@
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>all-users</t>
         </is>
@@ -5315,7 +6004,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>⚡ owner (分享自己拥有的资源)</t>
         </is>
@@ -5337,43 +6026,43 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>图例</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>✓ 全权</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>通过 {app}_admin_full 或具体 permission_group 放行，无资源级限制</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>⚡ owner/contrib/viewer</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>路径级放行，资源级 ACL 按 permission 梯度再过滤</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>路径级默认拒绝（Default Deny，无匹配 permission_group）</t>
         </is>
@@ -5458,7 +6147,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -5498,7 +6187,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I2" s="22" t="inlineStr">
+      <c r="I2" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -5510,7 +6199,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -5550,7 +6239,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -5562,7 +6251,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -5602,7 +6291,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I4" s="22" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -5614,7 +6303,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -5654,7 +6343,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -5666,7 +6355,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -5706,7 +6395,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -5714,7 +6403,7 @@
       <c r="J6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -5754,7 +6443,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -5766,7 +6455,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -5806,7 +6495,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -5814,7 +6503,7 @@
       <c r="J8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -5854,7 +6543,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -5862,7 +6551,7 @@
       <c r="J9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -5902,7 +6591,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="I10" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -5910,7 +6599,7 @@
       <c r="J10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -5950,7 +6639,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I11" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -5962,7 +6651,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6010,7 +6699,7 @@
       <c r="J12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6058,7 +6747,7 @@
       <c r="J13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6098,7 +6787,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="I14" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -6110,7 +6799,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6150,7 +6839,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I15" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -6158,7 +6847,7 @@
       <c r="J15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6198,7 +6887,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="I16" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -6210,7 +6899,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6262,7 +6951,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6302,7 +6991,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="I18" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -6314,7 +7003,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6354,7 +7043,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I19" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -6366,7 +7055,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6406,7 +7095,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="I20" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -6418,7 +7107,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6458,7 +7147,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I21" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -6470,7 +7159,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6510,7 +7199,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I22" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -6522,7 +7211,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6562,7 +7251,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="I23" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -6574,7 +7263,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6626,7 +7315,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6666,7 +7355,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="I25" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -6678,7 +7367,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6718,7 +7407,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I26" s="22" t="inlineStr">
+      <c r="I26" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -6730,7 +7419,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6770,7 +7459,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I27" s="22" t="inlineStr">
+      <c r="I27" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -6782,7 +7471,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6822,7 +7511,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I28" s="22" t="inlineStr">
+      <c r="I28" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -6834,7 +7523,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6886,7 +7575,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6934,7 +7623,7 @@
       <c r="J30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -6982,7 +7671,7 @@
       <c r="J31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7030,7 +7719,7 @@
       <c r="J32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7078,7 +7767,7 @@
       <c r="J33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7126,7 +7815,7 @@
       <c r="J34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="25" t="inlineStr">
+      <c r="A35" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7174,7 +7863,7 @@
       <c r="J35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="25" t="inlineStr">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7222,7 +7911,7 @@
       <c r="J36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="25" t="inlineStr">
+      <c r="A37" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7270,7 +7959,7 @@
       <c r="J37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="25" t="inlineStr">
+      <c r="A38" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7318,7 +8007,7 @@
       <c r="J38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="25" t="inlineStr">
+      <c r="A39" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7366,7 +8055,7 @@
       <c r="J39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="25" t="inlineStr">
+      <c r="A40" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7418,7 +8107,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="25" t="inlineStr">
+      <c r="A41" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7466,7 +8155,7 @@
       <c r="J41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="25" t="inlineStr">
+      <c r="A42" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7514,7 +8203,7 @@
       <c r="J42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="25" t="inlineStr">
+      <c r="A43" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7562,7 +8251,7 @@
       <c r="J43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="25" t="inlineStr">
+      <c r="A44" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7610,7 +8299,7 @@
       <c r="J44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="25" t="inlineStr">
+      <c r="A45" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7658,7 +8347,7 @@
       <c r="J45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="25" t="inlineStr">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7706,7 +8395,7 @@
       <c r="J46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="25" t="inlineStr">
+      <c r="A47" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7754,7 +8443,7 @@
       <c r="J47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="25" t="inlineStr">
+      <c r="A48" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7802,7 +8491,7 @@
       <c r="J48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="25" t="inlineStr">
+      <c r="A49" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7850,7 +8539,7 @@
       <c r="J49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="25" t="inlineStr">
+      <c r="A50" s="27" t="inlineStr">
         <is>
           <t>KB</t>
         </is>
@@ -7898,7 +8587,7 @@
       <c r="J50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="26" t="inlineStr">
+      <c r="A51" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -7950,7 +8639,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="26" t="inlineStr">
+      <c r="A52" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -7990,7 +8679,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I52" s="22" t="inlineStr">
+      <c r="I52" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -8002,7 +8691,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="26" t="inlineStr">
+      <c r="A53" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8042,7 +8731,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I53" s="22" t="inlineStr">
+      <c r="I53" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -8054,7 +8743,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="26" t="inlineStr">
+      <c r="A54" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8094,7 +8783,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I54" s="22" t="inlineStr">
+      <c r="I54" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -8106,7 +8795,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="26" t="inlineStr">
+      <c r="A55" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8146,7 +8835,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I55" s="22" t="inlineStr">
+      <c r="I55" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -8154,7 +8843,7 @@
       <c r="J55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="26" t="inlineStr">
+      <c r="A56" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8194,7 +8883,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I56" s="22" t="inlineStr">
+      <c r="I56" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -8202,7 +8891,7 @@
       <c r="J56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="26" t="inlineStr">
+      <c r="A57" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8242,7 +8931,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I57" s="22" t="inlineStr">
+      <c r="I57" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -8250,7 +8939,7 @@
       <c r="J57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="26" t="inlineStr">
+      <c r="A58" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8290,7 +8979,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I58" s="22" t="inlineStr">
+      <c r="I58" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -8298,7 +8987,7 @@
       <c r="J58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="26" t="inlineStr">
+      <c r="A59" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8338,7 +9027,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I59" s="22" t="inlineStr">
+      <c r="I59" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -8350,7 +9039,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="26" t="inlineStr">
+      <c r="A60" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8390,7 +9079,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I60" s="22" t="inlineStr">
+      <c r="I60" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -8402,7 +9091,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="26" t="inlineStr">
+      <c r="A61" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8450,7 +9139,7 @@
       <c r="J61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="26" t="inlineStr">
+      <c r="A62" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8490,7 +9179,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I62" s="27" t="inlineStr">
+      <c r="I62" s="29" t="inlineStr">
         <is>
           <t>⚠</t>
         </is>
@@ -8502,7 +9191,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="26" t="inlineStr">
+      <c r="A63" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8542,7 +9231,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I63" s="22" t="inlineStr">
+      <c r="I63" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -8554,7 +9243,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="26" t="inlineStr">
+      <c r="A64" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8594,7 +9283,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I64" s="22" t="inlineStr">
+      <c r="I64" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -8606,7 +9295,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="26" t="inlineStr">
+      <c r="A65" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8646,7 +9335,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I65" s="22" t="inlineStr">
+      <c r="I65" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -8658,7 +9347,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="26" t="inlineStr">
+      <c r="A66" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8698,7 +9387,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I66" s="22" t="inlineStr">
+      <c r="I66" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -8710,7 +9399,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="26" t="inlineStr">
+      <c r="A67" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8750,7 +9439,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I67" s="22" t="inlineStr">
+      <c r="I67" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -8762,7 +9451,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="26" t="inlineStr">
+      <c r="A68" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8802,7 +9491,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I68" s="22" t="inlineStr">
+      <c r="I68" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -8814,7 +9503,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="26" t="inlineStr">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8854,7 +9543,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I69" s="22" t="inlineStr">
+      <c r="I69" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -8862,7 +9551,7 @@
       <c r="J69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="26" t="inlineStr">
+      <c r="A70" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8902,7 +9591,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I70" s="22" t="inlineStr">
+      <c r="I70" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -8910,7 +9599,7 @@
       <c r="J70" s="5" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="26" t="inlineStr">
+      <c r="A71" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8950,7 +9639,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I71" s="22" t="inlineStr">
+      <c r="I71" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -8958,7 +9647,7 @@
       <c r="J71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="26" t="inlineStr">
+      <c r="A72" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -8998,7 +9687,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I72" s="22" t="inlineStr">
+      <c r="I72" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -9006,7 +9695,7 @@
       <c r="J72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="26" t="inlineStr">
+      <c r="A73" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9046,7 +9735,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I73" s="27" t="inlineStr">
+      <c r="I73" s="29" t="inlineStr">
         <is>
           <t>⚠</t>
         </is>
@@ -9058,7 +9747,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="26" t="inlineStr">
+      <c r="A74" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9098,7 +9787,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I74" s="22" t="inlineStr">
+      <c r="I74" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -9110,7 +9799,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="26" t="inlineStr">
+      <c r="A75" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9150,7 +9839,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I75" s="22" t="inlineStr">
+      <c r="I75" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -9158,7 +9847,7 @@
       <c r="J75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="26" t="inlineStr">
+      <c r="A76" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9198,7 +9887,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I76" s="22" t="inlineStr">
+      <c r="I76" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -9206,7 +9895,7 @@
       <c r="J76" s="5" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="26" t="inlineStr">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9246,7 +9935,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I77" s="22" t="inlineStr">
+      <c r="I77" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -9254,7 +9943,7 @@
       <c r="J77" s="5" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="26" t="inlineStr">
+      <c r="A78" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9294,7 +9983,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I78" s="22" t="inlineStr">
+      <c r="I78" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -9306,7 +9995,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="26" t="inlineStr">
+      <c r="A79" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9346,7 +10035,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I79" s="22" t="inlineStr">
+      <c r="I79" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -9354,7 +10043,7 @@
       <c r="J79" s="5" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="26" t="inlineStr">
+      <c r="A80" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9394,7 +10083,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I80" s="22" t="inlineStr">
+      <c r="I80" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -9406,7 +10095,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="26" t="inlineStr">
+      <c r="A81" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9446,7 +10135,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I81" s="22" t="inlineStr">
+      <c r="I81" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -9458,7 +10147,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="26" t="inlineStr">
+      <c r="A82" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9498,7 +10187,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I82" s="22" t="inlineStr">
+      <c r="I82" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -9510,7 +10199,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="26" t="inlineStr">
+      <c r="A83" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9550,7 +10239,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I83" s="22" t="inlineStr">
+      <c r="I83" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -9562,7 +10251,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="26" t="inlineStr">
+      <c r="A84" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9602,7 +10291,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I84" s="22" t="inlineStr">
+      <c r="I84" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -9614,7 +10303,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="26" t="inlineStr">
+      <c r="A85" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9654,7 +10343,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I85" s="22" t="inlineStr">
+      <c r="I85" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -9666,7 +10355,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="26" t="inlineStr">
+      <c r="A86" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9706,7 +10395,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I86" s="22" t="inlineStr">
+      <c r="I86" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -9718,7 +10407,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="26" t="inlineStr">
+      <c r="A87" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9758,7 +10447,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I87" s="22" t="inlineStr">
+      <c r="I87" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -9770,7 +10459,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="26" t="inlineStr">
+      <c r="A88" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9822,7 +10511,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="26" t="inlineStr">
+      <c r="A89" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9862,7 +10551,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I89" s="22" t="inlineStr">
+      <c r="I89" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -9874,7 +10563,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="26" t="inlineStr">
+      <c r="A90" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9914,7 +10603,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I90" s="22" t="inlineStr">
+      <c r="I90" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -9922,7 +10611,7 @@
       <c r="J90" s="5" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="26" t="inlineStr">
+      <c r="A91" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -9962,7 +10651,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I91" s="22" t="inlineStr">
+      <c r="I91" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -9974,7 +10663,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="26" t="inlineStr">
+      <c r="A92" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10014,7 +10703,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I92" s="22" t="inlineStr">
+      <c r="I92" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -10026,7 +10715,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="26" t="inlineStr">
+      <c r="A93" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10066,7 +10755,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I93" s="22" t="inlineStr">
+      <c r="I93" s="24" t="inlineStr">
         <is>
           <t>⚡</t>
         </is>
@@ -10078,7 +10767,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="26" t="inlineStr">
+      <c r="A94" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10126,7 +10815,7 @@
       <c r="J94" s="5" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="26" t="inlineStr">
+      <c r="A95" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10174,7 +10863,7 @@
       <c r="J95" s="5" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="26" t="inlineStr">
+      <c r="A96" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10222,7 +10911,7 @@
       <c r="J96" s="5" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="26" t="inlineStr">
+      <c r="A97" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10270,7 +10959,7 @@
       <c r="J97" s="5" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="26" t="inlineStr">
+      <c r="A98" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10318,7 +11007,7 @@
       <c r="J98" s="5" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="26" t="inlineStr">
+      <c r="A99" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10366,7 +11055,7 @@
       <c r="J99" s="5" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="26" t="inlineStr">
+      <c r="A100" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10414,7 +11103,7 @@
       <c r="J100" s="5" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="26" t="inlineStr">
+      <c r="A101" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10466,7 +11155,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="26" t="inlineStr">
+      <c r="A102" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10514,7 +11203,7 @@
       <c r="J102" s="5" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="26" t="inlineStr">
+      <c r="A103" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10562,7 +11251,7 @@
       <c r="J103" s="5" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="26" t="inlineStr">
+      <c r="A104" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10610,7 +11299,7 @@
       <c r="J104" s="5" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="26" t="inlineStr">
+      <c r="A105" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10658,7 +11347,7 @@
       <c r="J105" s="5" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="26" t="inlineStr">
+      <c r="A106" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10706,7 +11395,7 @@
       <c r="J106" s="5" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="26" t="inlineStr">
+      <c r="A107" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10754,7 +11443,7 @@
       <c r="J107" s="5" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="26" t="inlineStr">
+      <c r="A108" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10802,7 +11491,7 @@
       <c r="J108" s="5" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="26" t="inlineStr">
+      <c r="A109" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10850,7 +11539,7 @@
       <c r="J109" s="5" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="26" t="inlineStr">
+      <c r="A110" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10898,7 +11587,7 @@
       <c r="J110" s="5" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="26" t="inlineStr">
+      <c r="A111" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10946,7 +11635,7 @@
       <c r="J111" s="5" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="26" t="inlineStr">
+      <c r="A112" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -10994,7 +11683,7 @@
       <c r="J112" s="5" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="26" t="inlineStr">
+      <c r="A113" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -11042,7 +11731,7 @@
       <c r="J113" s="5" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="26" t="inlineStr">
+      <c r="A114" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -11090,7 +11779,7 @@
       <c r="J114" s="5" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="26" t="inlineStr">
+      <c r="A115" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -11138,7 +11827,7 @@
       <c r="J115" s="5" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="26" t="inlineStr">
+      <c r="A116" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -11186,7 +11875,7 @@
       <c r="J116" s="5" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="26" t="inlineStr">
+      <c r="A117" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -11234,7 +11923,7 @@
       <c r="J117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="26" t="inlineStr">
+      <c r="A118" s="28" t="inlineStr">
         <is>
           <t>Rubik</t>
         </is>
@@ -11282,7 +11971,7 @@
       <c r="J118" s="5" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="28" t="inlineStr">
+      <c r="A119" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -11330,7 +12019,7 @@
       <c r="J119" s="5" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="28" t="inlineStr">
+      <c r="A120" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -11378,7 +12067,7 @@
       <c r="J120" s="5" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="28" t="inlineStr">
+      <c r="A121" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -11426,7 +12115,7 @@
       <c r="J121" s="5" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="28" t="inlineStr">
+      <c r="A122" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -11474,7 +12163,7 @@
       <c r="J122" s="5" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="28" t="inlineStr">
+      <c r="A123" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -11522,7 +12211,7 @@
       <c r="J123" s="5" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="28" t="inlineStr">
+      <c r="A124" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -11574,7 +12263,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="28" t="inlineStr">
+      <c r="A125" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -11622,7 +12311,7 @@
       <c r="J125" s="5" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="28" t="inlineStr">
+      <c r="A126" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -11670,7 +12359,7 @@
       <c r="J126" s="5" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="28" t="inlineStr">
+      <c r="A127" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -11722,7 +12411,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="28" t="inlineStr">
+      <c r="A128" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -11770,7 +12459,7 @@
       <c r="J128" s="5" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="28" t="inlineStr">
+      <c r="A129" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -11818,7 +12507,7 @@
       <c r="J129" s="5" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="28" t="inlineStr">
+      <c r="A130" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -11870,7 +12559,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="28" t="inlineStr">
+      <c r="A131" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -11918,7 +12607,7 @@
       <c r="J131" s="5" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="28" t="inlineStr">
+      <c r="A132" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -11966,7 +12655,7 @@
       <c r="J132" s="5" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="28" t="inlineStr">
+      <c r="A133" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -12014,7 +12703,7 @@
       <c r="J133" s="5" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="28" t="inlineStr">
+      <c r="A134" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -12062,7 +12751,7 @@
       <c r="J134" s="5" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="28" t="inlineStr">
+      <c r="A135" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -12110,7 +12799,7 @@
       <c r="J135" s="5" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="28" t="inlineStr">
+      <c r="A136" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -12158,7 +12847,7 @@
       <c r="J136" s="5" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="28" t="inlineStr">
+      <c r="A137" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>
@@ -12210,7 +12899,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="28" t="inlineStr">
+      <c r="A138" s="30" t="inlineStr">
         <is>
           <t>Memory</t>
         </is>

--- a/diagrams/api-spec-v2.xlsx
+++ b/diagrams/api-spec-v2.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. IAM系统接口'!$A$1:$I$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. 权限点总表'!$A$1:$G$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. 业务接口权限矩阵'!$A$1:$J$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. 权限点总表'!$A$1:$G$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. 业务接口权限矩阵'!$A$1:$J$135</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3637,7 +3637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3802,12 +3802,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>kb_browse_knowledge_bases</t>
+          <t>kb_browse</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>KB 列表/单查/子路径读（含 mappings/files）</t>
+          <t>option1 读：知识库/目录映射/文件/文件系统（GET + POST 分页查询）</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -3827,78 +3827,50 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="A6" s="3" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>knowledgebase</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>kb_browse_conversations</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>会话列表/查询</t>
-        </is>
-      </c>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>/kb/conversations</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+          <t>/kb/knowledge_bases/files</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>6</v>
-      </c>
+      <c r="A7" s="3" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>knowledgebase</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>kb_browse_prompts</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>提示词只读（QA 场景要用）</t>
-        </is>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>/kb/prompts</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+          <t>/kb/knowledge_bases/files/history</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -3907,22 +3879,22 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>kb_file_download</t>
+          <t>kb_edit</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>文件下载（父 KB 继承）</t>
+          <t>option1 编辑：知识库/目录映射/文件 增删改</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/files/download</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>/kb/knowledge_bases/add</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -3932,62 +3904,38 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="A9" s="3" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>knowledgebase</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>kb_image_download</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>图片访问（父 KB 继承）</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>/kb/conversations/images/download</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+          <t>/kb/knowledge_bases/modify</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>9</v>
-      </c>
+      <c r="A10" s="3" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>knowledgebase</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>kb_create</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>KB 创建</t>
-        </is>
-      </c>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/add</t>
+          <t>/kb/knowledge_bases/remove</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -3995,34 +3943,20 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+      <c r="G10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="A11" s="3" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>knowledgebase</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>kb_modify</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>KB 修改（ACL contributor）</t>
-        </is>
-      </c>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/modify</t>
+          <t>/kb/knowledge_bases/mappings/add</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -4030,34 +3964,20 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+      <c r="G11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>11</v>
-      </c>
+      <c r="A12" s="3" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>knowledgebase</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>kb_remove</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>KB 删除（ACL owner）</t>
-        </is>
-      </c>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/remove</t>
+          <t>/kb/knowledge_bases/mappings/remove</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -4065,34 +3985,20 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+      <c r="G12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>12</v>
-      </c>
+      <c r="A13" s="3" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>knowledgebase</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>kb_mapping_write</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>目录映射写（/add, /remove）</t>
-        </is>
-      </c>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/mappings/</t>
+          <t>/kb/knowledge_bases/files/upload</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -4100,34 +4006,20 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+      <c r="G13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>13</v>
-      </c>
+      <c r="A14" s="3" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>knowledgebase</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>kb_file_upload</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>文件上传</t>
-        </is>
-      </c>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/files/upload</t>
+          <t>/kb/knowledge_bases/files/remove</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -4135,15 +4027,11 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+      <c r="G14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
@@ -4152,33 +4040,33 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>kb_file_delete</t>
+          <t>kb_model_view</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>文件删除</t>
+          <t>option2 读：模型配置查询</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/files/remove</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>/kb/models/config</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>all-users</t>
+          <t>kb-admins</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
@@ -4187,17 +4075,17 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>kb_conv_start</t>
+          <t>kb_model_edit</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>发起问答</t>
+          <t>option2 编辑：模型配置增删改</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>/kb/conversations/start</t>
+          <t>/kb/models/config/add</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -4207,67 +4095,43 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>all-users</t>
+          <t>kb-admins</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>16</v>
-      </c>
+      <c r="A17" s="3" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>knowledgebase</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>kb_conv_stop</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>停止问答</t>
-        </is>
-      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>/kb/conversations/stop</t>
-        </is>
-      </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+          <t>/kb/models/config/modify</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>17</v>
-      </c>
+      <c r="A18" s="3" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>knowledgebase</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>kb_conv_remove</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>删除会话</t>
-        </is>
-      </c>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>/kb/conversations/remove</t>
+          <t>/kb/models/config/remove</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -4275,15 +4139,11 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+      <c r="G18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
@@ -4292,22 +4152,22 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>kb_image_generate</t>
+          <t>kb_prompt_view</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>生成图片链接</t>
+          <t>option3 读：提示词查询（detail/options/page）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>/kb/conversations/images/generate</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>/kb/prompts/detail</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -4317,27 +4177,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>19</v>
-      </c>
+      <c r="A20" s="3" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>knowledgebase</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>kb_conv_query</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>历史对话 batch/single 查询</t>
-        </is>
-      </c>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>/kb/conversations/query/</t>
+          <t>/kb/prompts/options</t>
         </is>
       </c>
       <c r="F20" s="19" t="inlineStr">
@@ -4345,50 +4195,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+      <c r="G20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>20</v>
-      </c>
+      <c r="A21" s="3" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>knowledgebase</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>kb_retrieval</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>检索融合搜索</t>
-        </is>
-      </c>
+      <c r="C21" s="3" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>/kb/retrieval/fusion_search</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+          <t>/kb/prompts/page</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
@@ -4397,22 +4229,22 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>kb_filesystem_manage</t>
+          <t>kb_prompt_edit</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>文件系统管理（容器级，非 KB 级）</t>
+          <t>option3 编辑：提示词增删改</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/files/filesystem</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>ANY</t>
+          <t>/kb/prompts/add</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -4422,62 +4254,38 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>22</v>
-      </c>
+      <c r="A23" s="3" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>knowledgebase</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>kb_model_config_manage</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>模型配置管理</t>
-        </is>
-      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>/kb/models/config</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>ANY</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>kb-admins</t>
-        </is>
-      </c>
+          <t>/kb/prompts/modify</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>23</v>
-      </c>
+      <c r="A24" s="3" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>knowledgebase</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>kb_prompt_manage</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>提示词增删改</t>
-        </is>
-      </c>
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>/kb/prompts</t>
+          <t>/kb/prompts/remove</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -4485,15 +4293,11 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>kb-admins</t>
-        </is>
-      </c>
+      <c r="G24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
@@ -4502,12 +4306,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>kb_jargon_group_manage</t>
+          <t>kb_jargon_view</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>黑话库管理</t>
+          <t>option4 读：术语库/术语查询</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -4515,9 +4319,9 @@
           <t>/kb/jargon_groups</t>
         </is>
       </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>ANY</t>
+      <c r="F25" s="19" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -4527,97 +4331,73 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>25</v>
-      </c>
+      <c r="A26" s="3" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>knowledgebase</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>kb_jargon_manage</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>黑话条目管理</t>
-        </is>
-      </c>
+      <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>/kb/jargons</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>ANY</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>kb-admins</t>
-        </is>
-      </c>
+          <t>/kb/jargons_groups/jargon</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
+        <v>11</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>knowledgebase</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>rubik_admin_full</t>
+          <t>kb_jargon_edit</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Rubik 全应用访问</t>
+          <t>option4 编辑：术语库/术语增删改</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>/rubik/</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>ANY</t>
+          <t>/kb/jargon_groups/add</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>admins, rubik-admins</t>
+          <t>kb-admins</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>rubik_db_import</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>option1: 导入/删除数据库</t>
-        </is>
-      </c>
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>knowledgebase</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases</t>
+          <t>/kb/jargon_groups/remove</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -4625,269 +4405,237 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+      <c r="G28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr"/>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>knowledgebase</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="5" t="inlineStr"/>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/</t>
-        </is>
-      </c>
-      <c r="F29" s="21" t="inlineStr">
-        <is>
-          <t>DELETE</t>
+          <t>/kb/jargons/add</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>rubik_db_view</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>option2: 查看数据库</t>
-        </is>
-      </c>
+      <c r="A30" s="3" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>knowledgebase</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases</t>
-        </is>
-      </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+          <t>/kb/jargons/modify</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr"/>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>knowledgebase</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
       <c r="D31" s="5" t="inlineStr"/>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/</t>
-        </is>
-      </c>
-      <c r="F31" s="19" t="inlineStr">
+          <t>/kb/jargons/remove</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>knowledgebase</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>kb_conv_view</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>option5 读：对话列表/单查/图片访问</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>/kb/conversations/list</t>
+        </is>
+      </c>
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr"/>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="5" t="inlineStr"/>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>/rubik/api/databases/</t>
-        </is>
-      </c>
-      <c r="F32" s="20" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>all-users</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>knowledgebase</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>/kb/conversations</t>
+        </is>
+      </c>
+      <c r="F33" s="19" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>knowledgebase</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>/kb/conversations/images/download</t>
+        </is>
+      </c>
+      <c r="F34" s="19" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>knowledgebase</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>kb_conv_edit</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>option5 编辑：发起/停止问答 + 图片生成 + 删对话</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>/kb/conversations/start</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>rubik_db_data_dir</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>option2 敏感：数据目录</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>/rubik/api/databases/config/data-dir</t>
-        </is>
-      </c>
-      <c r="F33" s="19" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>rubik-admins</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>rubik_kb_build</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>option3: 知识库构建</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>/rubik/api/databases/</t>
-        </is>
-      </c>
-      <c r="F34" s="20" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>all-users</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>knowledgebase</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr"/>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>/kb/conversations/stop</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr"/>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="5" t="inlineStr"/>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>/rubik/api/databases/</t>
-        </is>
-      </c>
-      <c r="F35" s="19" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>rubik_knowledge_edit</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>option4: 知识增删</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>/rubik/api/databases/</t>
-        </is>
-      </c>
-      <c r="F36" s="22" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+      <c r="G36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr"/>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>knowledgebase</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
       <c r="D37" s="5" t="inlineStr"/>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/</t>
-        </is>
-      </c>
-      <c r="F37" s="21" t="inlineStr">
-        <is>
-          <t>DELETE</t>
+          <t>/kb/conversations/images/generate</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr"/>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>knowledgebase</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
       <c r="D38" s="5" t="inlineStr"/>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/</t>
+          <t>/kb/conversations/remove</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
@@ -4899,26 +4647,26 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
+        <v>14</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>knowledgebase</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>rubik_knowledge_special</t>
+          <t>kb_retrieval</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>option4 敏感：跨库特殊知识</t>
+          <t>option6: 融合检索</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/knowledge/special</t>
+          <t>/kb/retrieval/fusion_search</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
@@ -4928,57 +4676,57 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>rubik-admins</t>
+          <t>all-users</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
+        <v>15</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>knowledgebase</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>rubik_knowledge_view</t>
+          <t>kb_jargon_bind</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>option5: 知识查看</t>
+          <t>option7: 知识库-术语库关联（绑定/解绑）</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/</t>
-        </is>
-      </c>
-      <c r="F40" s="19" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>/kb/jargon_groups/knowledge_bases/add</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>all-users</t>
+          <t>kb-admins</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr"/>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>knowledgebase</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
       <c r="D41" s="5" t="inlineStr"/>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/</t>
+          <t>/kb/jargon_groups/knowledge_bases/remove</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
@@ -4990,7 +4738,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
@@ -4999,141 +4747,141 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>rubik_skill_manage</t>
+          <t>rubik_admin_full</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>option6: 技能管理</t>
+          <t>Rubik 全应用访问</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
+          <t>/rubik/</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>admins, rubik-admins</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>rubik_db_import</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>option1: 导入/删除数据库</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>/rubik/api/databases</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>all-users</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr"/>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
           <t>/rubik/api/databases/</t>
         </is>
       </c>
-      <c r="F42" s="20" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="F44" s="21" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>rubik_db_view</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>option2: 查看数据库</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>/rubik/api/databases</t>
+        </is>
+      </c>
+      <c r="F45" s="19" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>all-users</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr"/>
-      <c r="B43" s="9" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr"/>
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>rubik</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="5" t="inlineStr"/>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr"/>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>/rubik/api/databases/</t>
         </is>
       </c>
-      <c r="F43" s="22" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>rubik_metadata</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>option7: 数据库元数据管理</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>/rubik/api/metadata/</t>
-        </is>
-      </c>
-      <c r="F44" s="19" t="inlineStr">
+      <c r="F46" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr"/>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="5" t="inlineStr"/>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>/rubik/api/metadata/</t>
-        </is>
-      </c>
-      <c r="F45" s="22" t="inlineStr">
-        <is>
-          <t>PUT</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>rubik_query</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>option8: 问数/会话</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>/rubik/api/query</t>
-        </is>
-      </c>
-      <c r="F46" s="20" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+      <c r="G46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr"/>
@@ -5146,57 +4894,85 @@
       <c r="D47" s="5" t="inlineStr"/>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/sessions</t>
-        </is>
-      </c>
-      <c r="F47" s="19" t="inlineStr">
+          <t>/rubik/api/databases/</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>rubik_db_data_dir</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>option2 敏感：数据目录</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>/rubik/api/databases/config/data-dir</t>
+        </is>
+      </c>
+      <c r="F48" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr"/>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>rubik-admins</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>rubik</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr"/>
-      <c r="D48" s="5" t="inlineStr"/>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>/rubik/api/sessions</t>
-        </is>
-      </c>
-      <c r="F48" s="20" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>rubik_kb_build</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>option3: 知识库构建</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>/rubik/api/databases/</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr"/>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr"/>
-      <c r="D49" s="5" t="inlineStr"/>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>/rubik/api/sessions/</t>
-        </is>
-      </c>
-      <c r="F49" s="19" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr"/>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>all-users</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr"/>
@@ -5209,71 +4985,71 @@
       <c r="D50" s="5" t="inlineStr"/>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/sessions/</t>
-        </is>
-      </c>
-      <c r="F50" s="20" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>/rubik/api/databases/</t>
+        </is>
+      </c>
+      <c r="F50" s="19" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr"/>
+      <c r="A51" s="3" t="n">
+        <v>21</v>
+      </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
           <t>rubik</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="5" t="inlineStr"/>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>rubik_knowledge_edit</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>option4: 知识增删</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/sessions/</t>
-        </is>
-      </c>
-      <c r="F51" s="21" t="inlineStr">
+          <t>/rubik/api/databases/</t>
+        </is>
+      </c>
+      <c r="F51" s="22" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>all-users</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr"/>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr"/>
+      <c r="D52" s="5" t="inlineStr"/>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>/rubik/api/databases/</t>
+        </is>
+      </c>
+      <c r="F52" s="21" t="inlineStr">
         <is>
           <t>DELETE</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>rubik</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>rubik_config_view</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>option9 读：配置查询</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>/rubik/api/config</t>
-        </is>
-      </c>
-      <c r="F52" s="19" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+      <c r="G52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr"/>
@@ -5286,19 +5062,19 @@
       <c r="D53" s="5" t="inlineStr"/>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/</t>
-        </is>
-      </c>
-      <c r="F53" s="19" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>/rubik/api/databases/</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
@@ -5307,22 +5083,22 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>rubik_config_manage</t>
+          <t>rubik_knowledge_special</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>option9 写：配置管理</t>
+          <t>option4 敏感：跨库特殊知识</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/</t>
-        </is>
-      </c>
-      <c r="F54" s="22" t="inlineStr">
-        <is>
-          <t>PUT</t>
+          <t>/rubik/api/databases/knowledge/special</t>
+        </is>
+      </c>
+      <c r="F54" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -5332,25 +5108,39 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr"/>
+      <c r="A55" s="3" t="n">
+        <v>23</v>
+      </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
           <t>rubik</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr"/>
-      <c r="D55" s="5" t="inlineStr"/>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>rubik_knowledge_view</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>option5: 知识查看</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/</t>
-        </is>
-      </c>
-      <c r="F55" s="20" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr"/>
+          <t>/rubik/api/databases/</t>
+        </is>
+      </c>
+      <c r="F55" s="19" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>all-users</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr"/>
@@ -5363,19 +5153,19 @@
       <c r="D56" s="5" t="inlineStr"/>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/</t>
-        </is>
-      </c>
-      <c r="F56" s="21" t="inlineStr">
-        <is>
-          <t>DELETE</t>
+          <t>/rubik/api/databases/</t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
@@ -5384,22 +5174,22 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>rubik_dashboard_view</t>
+          <t>rubik_skill_manage</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>option10: 查看仪表盘</t>
+          <t>option6: 技能管理</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/dashboards</t>
-        </is>
-      </c>
-      <c r="F57" s="19" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>/rubik/api/databases/</t>
+        </is>
+      </c>
+      <c r="F57" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -5419,19 +5209,19 @@
       <c r="D58" s="5" t="inlineStr"/>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/dashboards/</t>
-        </is>
-      </c>
-      <c r="F58" s="19" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>/rubik/api/databases/</t>
+        </is>
+      </c>
+      <c r="F58" s="22" t="inlineStr">
+        <is>
+          <t>PUT</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
@@ -5440,22 +5230,22 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>rubik_dashboard_edit</t>
+          <t>rubik_metadata</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>option11: 增删仪表盘</t>
+          <t>option7: 数据库元数据管理</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/dashboards</t>
-        </is>
-      </c>
-      <c r="F59" s="20" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>/rubik/api/metadata/</t>
+        </is>
+      </c>
+      <c r="F59" s="19" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -5475,7 +5265,7 @@
       <c r="D60" s="5" t="inlineStr"/>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/dashboards/</t>
+          <t>/rubik/api/metadata/</t>
         </is>
       </c>
       <c r="F60" s="22" t="inlineStr">
@@ -5486,48 +5276,52 @@
       <c r="G60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr"/>
+      <c r="A61" s="3" t="n">
+        <v>26</v>
+      </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
           <t>rubik</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr"/>
-      <c r="D61" s="5" t="inlineStr"/>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>rubik_query</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>option8: 问数/会话</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/dashboards/</t>
-        </is>
-      </c>
-      <c r="F61" s="21" t="inlineStr">
-        <is>
-          <t>DELETE</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr"/>
+          <t>/rubik/api/query</t>
+        </is>
+      </c>
+      <c r="F61" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>all-users</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
-        <v>41</v>
-      </c>
+      <c r="A62" s="3" t="inlineStr"/>
       <c r="B62" s="9" t="inlineStr">
         <is>
           <t>rubik</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>rubik_db_refresh</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>default: 数据库刷新</t>
-        </is>
-      </c>
+      <c r="C62" s="3" t="inlineStr"/>
+      <c r="D62" s="5" t="inlineStr"/>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/refresh/</t>
+          <t>/rubik/api/sessions</t>
         </is>
       </c>
       <c r="F62" s="19" t="inlineStr">
@@ -5535,11 +5329,7 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+      <c r="G62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr"/>
@@ -5552,7 +5342,7 @@
       <c r="D63" s="5" t="inlineStr"/>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/refresh/</t>
+          <t>/rubik/api/sessions</t>
         </is>
       </c>
       <c r="F63" s="20" t="inlineStr">
@@ -5563,224 +5353,609 @@
       <c r="G63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>memory_admin_full</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>Memory 全应用访问 — admins 专属（含 POST /tenants 与 /system/recovery 等超管动作）</t>
-        </is>
-      </c>
+      <c r="A64" s="3" t="inlineStr"/>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr"/>
+      <c r="D64" s="5" t="inlineStr"/>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>/memory/</t>
-        </is>
-      </c>
-      <c r="F64" s="18" t="inlineStr">
-        <is>
-          <t>ANY</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>admins</t>
-        </is>
-      </c>
+          <t>/rubik/api/sessions/</t>
+        </is>
+      </c>
+      <c r="F64" s="19" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>memory_tenant_admin</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>租户管理：/tenants/* 子路径（trailing-/ 排除 POST /tenants） + /templates* 全部 + /memory/* 数据</t>
-        </is>
-      </c>
+      <c r="A65" s="3" t="inlineStr"/>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr"/>
+      <c r="D65" s="5" t="inlineStr"/>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/tenants/</t>
-        </is>
-      </c>
-      <c r="F65" s="18" t="inlineStr">
-        <is>
-          <t>ANY</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>memory-admins</t>
-        </is>
-      </c>
+          <t>/rubik/api/sessions/</t>
+        </is>
+      </c>
+      <c r="F65" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr"/>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>memory</t>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr"/>
       <c r="D66" s="5" t="inlineStr"/>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/templates</t>
-        </is>
-      </c>
-      <c r="F66" s="18" t="inlineStr">
-        <is>
-          <t>ANY</t>
+          <t>/rubik/api/sessions/</t>
+        </is>
+      </c>
+      <c r="F66" s="21" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr"/>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr"/>
-      <c r="D67" s="5" t="inlineStr"/>
+      <c r="A67" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>rubik_config_view</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>option9 读：配置查询</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/memory/</t>
-        </is>
-      </c>
-      <c r="F67" s="18" t="inlineStr">
-        <is>
-          <t>ANY</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr"/>
+          <t>/rubik/api/config</t>
+        </is>
+      </c>
+      <c r="F67" s="19" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>all-users</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>memory</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>memory_user_data</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>数据面：记忆增删改查（add/query/update/delete）</t>
-        </is>
-      </c>
+      <c r="A68" s="3" t="inlineStr"/>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr"/>
+      <c r="D68" s="5" t="inlineStr"/>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/memory/</t>
-        </is>
-      </c>
-      <c r="F68" s="18" t="inlineStr">
-        <is>
-          <t>ANY</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>all-users</t>
-        </is>
-      </c>
+          <t>/rubik/api/config/</t>
+        </is>
+      </c>
+      <c r="F68" s="19" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
+        <v>28</v>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>rubik_config_manage</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>option9 写：配置管理</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>/rubik/api/config/</t>
+        </is>
+      </c>
+      <c r="F69" s="22" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>rubik-admins</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr"/>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr"/>
+      <c r="D70" s="5" t="inlineStr"/>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>/rubik/api/config/</t>
+        </is>
+      </c>
+      <c r="F70" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr"/>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr"/>
+      <c r="D71" s="5" t="inlineStr"/>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>/rubik/api/config/</t>
+        </is>
+      </c>
+      <c r="F71" s="21" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>rubik_dashboard_view</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>option10: 查看仪表盘</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>/rubik/api/dashboards</t>
+        </is>
+      </c>
+      <c r="F72" s="19" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>all-users</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr"/>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr"/>
+      <c r="D73" s="5" t="inlineStr"/>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>/rubik/api/dashboards/</t>
+        </is>
+      </c>
+      <c r="F73" s="19" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>rubik_dashboard_edit</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>option11: 增删仪表盘</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>/rubik/api/dashboards</t>
+        </is>
+      </c>
+      <c r="F74" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>all-users</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr"/>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr"/>
+      <c r="D75" s="5" t="inlineStr"/>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>/rubik/api/dashboards/</t>
+        </is>
+      </c>
+      <c r="F75" s="22" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr"/>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr"/>
+      <c r="D76" s="5" t="inlineStr"/>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>/rubik/api/dashboards/</t>
+        </is>
+      </c>
+      <c r="F76" s="21" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>rubik_db_refresh</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>default: 数据库刷新</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>/rubik/api/refresh/</t>
+        </is>
+      </c>
+      <c r="F77" s="19" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>all-users</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr"/>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>rubik</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr"/>
+      <c r="D78" s="5" t="inlineStr"/>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>/rubik/api/refresh/</t>
+        </is>
+      </c>
+      <c r="F78" s="20" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>memory</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>memory_admin_full</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Memory 全应用访问 — admins 专属（含 POST /tenants 与 /system/recovery 等超管动作）</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>/memory/</t>
+        </is>
+      </c>
+      <c r="F79" s="18" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>admins</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>memory_tenant_admin</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>租户管理：/tenants/* 子路径（trailing-/ 排除 POST /tenants） + /templates* 全部 + /memory/* 数据</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>/memory/api/v1/tenants/</t>
+        </is>
+      </c>
+      <c r="F80" s="18" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>memory-admins</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr"/>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr"/>
+      <c r="D81" s="5" t="inlineStr"/>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>/memory/api/v1/templates</t>
+        </is>
+      </c>
+      <c r="F81" s="18" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr"/>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr"/>
+      <c r="D82" s="5" t="inlineStr"/>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>/memory/api/v1/memory/</t>
+        </is>
+      </c>
+      <c r="F82" s="18" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>memory_user_data</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>数据面：记忆增删改查（add/query/update/delete）</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>/memory/api/v1/memory/</t>
+        </is>
+      </c>
+      <c r="F83" s="18" t="inlineStr">
+        <is>
+          <t>ANY</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>all-users</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>memory</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>memory_user_templates_read</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>数据面：模板只读（末端用户查看已生效模板）</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>/memory/api/v1/templates</t>
         </is>
       </c>
-      <c r="F69" s="19" t="inlineStr">
+      <c r="F84" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="G84" s="5" t="inlineStr">
         <is>
           <t>all-users</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>memory</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>memory_health</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>数据面：健康检查</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="E85" s="5" t="inlineStr">
         <is>
           <t>/memory/api/v1/health</t>
         </is>
       </c>
-      <c r="F70" s="19" t="inlineStr">
+      <c r="F85" s="19" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="G85" s="5" t="inlineStr">
         <is>
           <t>all-users</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G70"/>
+  <autoFilter ref="A1:G85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6079,7 +6254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J138"/>
+  <dimension ref="A1:J135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6154,7 +6329,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>kb_browse_knowledge_bases</t>
+          <t>kb_browse</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -6206,7 +6381,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>kb_browse_knowledge_bases</t>
+          <t>kb_browse</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -6244,11 +6419,7 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>X-Allowed-Ids 过滤</t>
-        </is>
-      </c>
+      <c r="J3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="27" t="inlineStr">
@@ -6258,7 +6429,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>kb_browse_knowledge_bases</t>
+          <t>kb_browse</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -6298,7 +6469,7 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>?KDSID=... viewer</t>
+          <t>?kbs_id=... viewer</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6481,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>kb_browse_knowledge_bases</t>
+          <t>kb_browse</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -6362,7 +6533,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>kb_browse_knowledge_bases</t>
+          <t>kb_browse</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -6410,12 +6581,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>kb_browse_knowledge_bases</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>kb_browse</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -6450,7 +6621,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>viewer on kb</t>
+          <t>分页查询 (body.kbs_id)</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6633,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>kb_browse_knowledge_bases</t>
+          <t>kb_browse</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -6472,7 +6643,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/files/history</t>
+          <t>/kb/knowledge_bases/files/count</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -6510,17 +6681,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>kb_browse_knowledge_bases</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>kb_browse</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/files/count</t>
+          <t>/kb/knowledge_bases/files/history</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -6548,7 +6719,11 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>入库历史</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="27" t="inlineStr">
@@ -6558,7 +6733,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>kb_browse_knowledge_bases</t>
+          <t>kb_browse</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -6568,7 +6743,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/{kb_name}/jargon</t>
+          <t>/kb/knowledge_bases/files/filesystem</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -6596,7 +6771,11 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>暂未支持</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="27" t="inlineStr">
@@ -6606,7 +6785,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>kb_file_download</t>
+          <t>kb_browse</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -6616,7 +6795,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/files/download</t>
+          <t>/kb/knowledge_bases/jargon_groups</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -6646,7 +6825,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>viewer 继承父 KB</t>
+          <t>指定 KB 绑定的术语库</t>
         </is>
       </c>
     </row>
@@ -6658,17 +6837,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>kb_browse_prompts</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>kb_edit</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>/kb/prompts</t>
+          <t>/kb/knowledge_bases/add</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -6696,7 +6875,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>创建者成 owner</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="27" t="inlineStr">
@@ -6706,17 +6889,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>kb_browse_prompts</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>kb_edit</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>/kb/prompts/menu</t>
+          <t>/kb/knowledge_bases/modify</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -6739,12 +6922,16 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr"/>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="27" t="inlineStr">
@@ -6754,17 +6941,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>kb_browse_conversations</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>kb_edit</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>/kb/conversations/query/batch</t>
+          <t>/kb/knowledge_bases/remove</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -6794,7 +6981,7 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>只看自己的</t>
+          <t>owner, ACL 级联删</t>
         </is>
       </c>
     </row>
@@ -6806,17 +6993,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>kb_browse_conversations</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>kb_edit</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>/kb/conversations/query/single</t>
+          <t>/kb/knowledge_bases/mappings/add</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -6844,7 +7031,11 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
@@ -6854,17 +7045,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>kb_image_download</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>kb_edit</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>/kb/conversations/images/download</t>
+          <t>/kb/knowledge_bases/mappings/remove</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -6894,7 +7085,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>viewer 继承父 KB</t>
+          <t>contributor</t>
         </is>
       </c>
     </row>
@@ -6906,7 +7097,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>kb_create</t>
+          <t>kb_edit</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -6916,7 +7107,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/add</t>
+          <t>/kb/knowledge_bases/files/upload</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -6939,14 +7130,14 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>⚡</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>创建者成 owner</t>
+          <t>contributor</t>
         </is>
       </c>
     </row>
@@ -6958,7 +7149,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>kb_modify</t>
+          <t>kb_edit</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -6968,7 +7159,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/modify</t>
+          <t>/kb/knowledge_bases/files/remove</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -7010,17 +7201,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>kb_remove</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>kb_model_view</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/remove</t>
+          <t>/kb/models/config</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -7043,16 +7234,12 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I19" s="24" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>owner, ACL 级联删</t>
-        </is>
-      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
@@ -7062,7 +7249,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>kb_mapping_write</t>
+          <t>kb_model_edit</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -7072,7 +7259,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/mappings/add</t>
+          <t>/kb/models/config/add</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -7095,16 +7282,12 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I20" s="24" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>contributor</t>
-        </is>
-      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="27" t="inlineStr">
@@ -7114,7 +7297,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>kb_mapping_write</t>
+          <t>kb_model_edit</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -7124,7 +7307,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/mappings/remove</t>
+          <t>/kb/models/config/modify</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -7147,16 +7330,12 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I21" s="24" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>contributor</t>
-        </is>
-      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="27" t="inlineStr">
@@ -7166,7 +7345,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>kb_file_upload</t>
+          <t>kb_model_edit</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -7176,7 +7355,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/files/upload</t>
+          <t>/kb/models/config/remove</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -7199,16 +7378,12 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I22" s="24" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>contributor</t>
-        </is>
-      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="27" t="inlineStr">
@@ -7218,17 +7393,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>kb_file_delete</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>kb_prompt_view</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/files/remove</t>
+          <t>/kb/prompts/detail</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -7251,16 +7426,12 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I23" s="24" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>contributor</t>
-        </is>
-      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="27" t="inlineStr">
@@ -7270,17 +7441,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>kb_conv_start</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>kb_prompt_view</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>/kb/conversations/start</t>
+          <t>/kb/prompts/options</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -7308,11 +7479,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>创建 conversation</t>
-        </is>
-      </c>
+      <c r="J24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="27" t="inlineStr">
@@ -7322,7 +7489,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>kb_conv_stop</t>
+          <t>kb_prompt_view</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -7332,7 +7499,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>/kb/conversations/stop</t>
+          <t>/kb/prompts/page</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -7355,16 +7522,12 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I25" s="24" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="27" t="inlineStr">
@@ -7374,7 +7537,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>kb_conv_remove</t>
+          <t>kb_prompt_edit</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -7384,7 +7547,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>/kb/conversations/remove</t>
+          <t>/kb/prompts/add</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -7407,16 +7570,12 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I26" s="24" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="27" t="inlineStr">
@@ -7426,7 +7585,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>kb_image_generate</t>
+          <t>kb_prompt_edit</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -7436,7 +7595,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>/kb/conversations/images/generate</t>
+          <t>/kb/prompts/modify</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -7459,16 +7618,12 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I27" s="24" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>viewer</t>
-        </is>
-      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="27" t="inlineStr">
@@ -7478,7 +7633,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>kb_retrieval</t>
+          <t>kb_prompt_edit</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -7488,7 +7643,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>/kb/retrieval/fusion_search</t>
+          <t>/kb/prompts/remove</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -7511,16 +7666,12 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I28" s="24" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>viewer</t>
-        </is>
-      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="27" t="inlineStr">
@@ -7530,7 +7681,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>kb_filesystem_manage</t>
+          <t>kb_jargon_view</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -7540,7 +7691,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/files/filesystem</t>
+          <t>/kb/jargon_groups</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -7568,11 +7719,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>容器级</t>
-        </is>
-      </c>
+      <c r="J29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="27" t="inlineStr">
@@ -7582,17 +7729,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>kb_filesystem_manage</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>kb_jargon_view</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/files/filesystem/add</t>
+          <t>/kb/jargon_groups/jargons</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -7630,17 +7777,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>kb_filesystem_manage</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>kb_jargon_view</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>/kb/knowledge_bases/files/filesystem/remove</t>
+          <t>/kb/jargon_groups/version</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -7678,7 +7825,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>kb_model_config_manage</t>
+          <t>kb_jargon_view</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -7688,7 +7835,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>/kb/models/config</t>
+          <t>/kb/jargons_groups/jargon</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -7716,7 +7863,11 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>api.md 拼写即如此</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="27" t="inlineStr">
@@ -7726,17 +7877,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>kb_model_config_manage</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>kb_jargon_edit</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>/kb/models/config/set</t>
+          <t>/kb/jargon_groups/add</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -7774,7 +7925,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>kb_model_config_manage</t>
+          <t>kb_jargon_edit</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -7784,7 +7935,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>/kb/models/config/add</t>
+          <t>/kb/jargon_groups/remove</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -7822,7 +7973,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>kb_model_config_manage</t>
+          <t>kb_jargon_edit</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -7832,7 +7983,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>/kb/models/config/modify</t>
+          <t>/kb/jargons/add</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -7870,7 +8021,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>kb_model_config_manage</t>
+          <t>kb_jargon_edit</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -7880,7 +8031,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>/kb/models/config/remove</t>
+          <t>/kb/jargons/modify</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -7918,7 +8069,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>kb_prompt_manage</t>
+          <t>kb_jargon_edit</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -7928,7 +8079,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>/kb/prompts/add</t>
+          <t>/kb/jargons/remove</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -7966,17 +8117,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>kb_prompt_manage</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>kb_conv_view</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>/kb/prompts/modify</t>
+          <t>/kb/conversations/list</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -7999,12 +8150,16 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr"/>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>暂未支持</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="27" t="inlineStr">
@@ -8014,17 +8169,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>kb_prompt_manage</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>kb_conv_view</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>/kb/prompts/remove</t>
+          <t>/kb/conversations</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -8047,12 +8202,16 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr"/>
+      <c r="I39" s="24" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>单对话，暂未支持</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="27" t="inlineStr">
@@ -8062,17 +8221,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>kb_prompt_manage</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>kb_conv_view</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>/kb/prompts/page</t>
+          <t>/kb/conversations/images/download</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -8095,14 +8254,14 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="I40" s="24" t="inlineStr">
+        <is>
+          <t>⚡</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>分页（POST 归为 kb-admins，注意）</t>
+          <t>viewer 继承父 KB</t>
         </is>
       </c>
     </row>
@@ -8114,17 +8273,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>kb_jargon_group_manage</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>kb_conv_edit</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>/kb/jargon_groups</t>
+          <t>/kb/conversations/start</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -8147,12 +8306,16 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>创建 conversation</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="27" t="inlineStr">
@@ -8162,17 +8325,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>kb_jargon_group_manage</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>kb_conv_edit</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>/kb/jargon_groups/jargons</t>
+          <t>/kb/conversations/stop</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -8195,12 +8358,16 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr"/>
+      <c r="I42" s="24" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="27" t="inlineStr">
@@ -8210,17 +8377,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>kb_jargon_group_manage</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>kb_conv_edit</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>/kb/jargon_groups/version/{id}</t>
+          <t>/kb/conversations/remove</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -8243,12 +8410,16 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr"/>
+      <c r="I43" s="24" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>owner, 暂未支持</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="27" t="inlineStr">
@@ -8258,7 +8429,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>kb_jargon_group_manage</t>
+          <t>kb_conv_edit</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -8268,7 +8439,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>/kb/jargon_groups/add</t>
+          <t>/kb/conversations/images/generate</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -8291,12 +8462,16 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="J44" s="5" t="inlineStr"/>
+      <c r="I44" s="24" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="27" t="inlineStr">
@@ -8306,7 +8481,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>kb_jargon_group_manage</t>
+          <t>kb_retrieval</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -8316,7 +8491,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>/kb/jargon_groups/remove</t>
+          <t>/kb/retrieval/fusion_search</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -8339,12 +8514,16 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr"/>
+      <c r="I45" s="24" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>viewer on kds_list</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="27" t="inlineStr">
@@ -8354,7 +8533,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>kb_jargon_group_manage</t>
+          <t>kb_jargon_bind</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -8402,7 +8581,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>kb_jargon_group_manage</t>
+          <t>kb_jargon_bind</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -8443,14 +8622,14 @@
       <c r="J47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="27" t="inlineStr">
-        <is>
-          <t>KB</t>
+      <c r="A48" s="28" t="inlineStr">
+        <is>
+          <t>Rubik</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>kb_jargon_manage</t>
+          <t>rubik_db_import</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -8460,7 +8639,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>/kb/jargons/add</t>
+          <t>/rubik/api/databases</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -8468,14 +8647,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -8483,32 +8662,36 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>创建→owner</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="27" t="inlineStr">
-        <is>
-          <t>KB</t>
+      <c r="A49" s="28" t="inlineStr">
+        <is>
+          <t>Rubik</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>kb_jargon_manage</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>rubik_db_import</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>/kb/jargons/modify</t>
+          <t>/rubik/api/databases/{id}</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -8516,14 +8699,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -8531,32 +8714,36 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr"/>
+      <c r="I49" s="24" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="27" t="inlineStr">
-        <is>
-          <t>KB</t>
+      <c r="A50" s="28" t="inlineStr">
+        <is>
+          <t>Rubik</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>kb_jargon_manage</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>rubik_db_view</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>/kb/jargons/remove</t>
+          <t>/rubik/api/databases</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -8564,14 +8751,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -8579,12 +8766,16 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr"/>
+      <c r="I50" s="24" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>X-Allowed-Ids</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="28" t="inlineStr">
@@ -8594,17 +8785,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>rubik_db_import</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>rubik_db_view</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases</t>
+          <t>/rubik/api/databases/{id}</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -8627,14 +8818,14 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="I51" s="24" t="inlineStr">
+        <is>
+          <t>⚡</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>创建→owner</t>
+          <t>viewer</t>
         </is>
       </c>
     </row>
@@ -8646,17 +8837,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>rubik_db_import</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>DELETE</t>
+          <t>rubik_db_view</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}</t>
+          <t>/rubik/api/databases/{id}/check</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -8684,11 +8875,7 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
+      <c r="J52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="28" t="inlineStr">
@@ -8708,7 +8895,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases</t>
+          <t>/rubik/api/databases/{id}/schema</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -8736,11 +8923,7 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>X-Allowed-Ids</t>
-        </is>
-      </c>
+      <c r="J53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="28" t="inlineStr">
@@ -8760,7 +8943,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}</t>
+          <t>/rubik/api/databases/{id}/tables-columns</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -8788,11 +8971,7 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>viewer</t>
-        </is>
-      </c>
+      <c r="J54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="28" t="inlineStr">
@@ -8812,7 +8991,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/check</t>
+          <t>/rubik/api/databases/{id}/tables/{name}</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -8853,14 +9032,14 @@
           <t>rubik_db_view</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/schema</t>
+          <t>/rubik/api/databases/{id}/prettify-sql</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -8888,7 +9067,11 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J56" s="5" t="inlineStr"/>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="28" t="inlineStr">
@@ -8901,14 +9084,14 @@
           <t>rubik_db_view</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/tables-columns</t>
+          <t>/rubik/api/databases/{id}/execute-sql</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -8936,7 +9119,11 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J57" s="5" t="inlineStr"/>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="28" t="inlineStr">
@@ -8949,14 +9136,14 @@
           <t>rubik_db_view</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/tables/{name}</t>
+          <t>/rubik/api/databases/test</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -8979,9 +9166,9 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I58" s="24" t="inlineStr">
-        <is>
-          <t>⚡</t>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr"/>
@@ -8994,17 +9181,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>rubik_db_view</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>rubik_db_data_dir</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/prettify-sql</t>
+          <t>/rubik/api/databases/config/data-dir</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -9027,14 +9214,14 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I59" s="24" t="inlineStr">
-        <is>
-          <t>⚡</t>
+      <c r="I59" s="29" t="inlineStr">
+        <is>
+          <t>⚠</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>viewer</t>
+          <t>理想 rubik-admins only；OR 语义下被 rubik_db_view GET 覆盖（已知限制）</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9233,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>rubik_db_view</t>
+          <t>rubik_kb_build</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -9056,7 +9243,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/execute-sql</t>
+          <t>/rubik/api/databases/{id}/build</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -9098,7 +9285,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>rubik_db_view</t>
+          <t>rubik_kb_build</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -9108,7 +9295,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/test</t>
+          <t>/rubik/api/databases/{id}/build/stream</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -9131,12 +9318,16 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J61" s="5" t="inlineStr"/>
+      <c r="I61" s="24" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="28" t="inlineStr">
@@ -9146,17 +9337,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>rubik_db_data_dir</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>rubik_kb_build</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/config/data-dir</t>
+          <t>/rubik/api/databases/{id}/build/cancel</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -9179,14 +9370,14 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I62" s="29" t="inlineStr">
-        <is>
-          <t>⚠</t>
+      <c r="I62" s="24" t="inlineStr">
+        <is>
+          <t>⚡</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>理想 rubik-admins only；OR 语义下被 rubik_db_view GET 覆盖（已知限制）</t>
+          <t>contributor</t>
         </is>
       </c>
     </row>
@@ -9201,14 +9392,14 @@
           <t>rubik_kb_build</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/build</t>
+          <t>/rubik/api/databases/{id}/build/status</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -9238,7 +9429,7 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>contributor</t>
+          <t>viewer</t>
         </is>
       </c>
     </row>
@@ -9250,17 +9441,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>rubik_kb_build</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>rubik_knowledge_edit</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/build/stream</t>
+          <t>/rubik/api/databases/{id}/knowledge/{type}/{item}</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -9302,17 +9493,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>rubik_kb_build</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>rubik_knowledge_edit</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/build/cancel</t>
+          <t>/rubik/api/databases/{id}/knowledge/{type}/{item}</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -9354,17 +9545,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>rubik_kb_build</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>rubik_knowledge_edit</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/build/status</t>
+          <t>/rubik/api/databases/{id}/knowledge/taxonomy</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -9392,11 +9583,7 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J66" s="5" t="inlineStr">
-        <is>
-          <t>viewer</t>
-        </is>
-      </c>
+      <c r="J66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="28" t="inlineStr">
@@ -9409,14 +9596,14 @@
           <t>rubik_knowledge_edit</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>PUT</t>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/knowledge/{type}/{item}</t>
+          <t>/rubik/api/databases/{id}/knowledge/custom</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -9444,11 +9631,7 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J67" s="5" t="inlineStr">
-        <is>
-          <t>contributor</t>
-        </is>
-      </c>
+      <c r="J67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="28" t="inlineStr">
@@ -9461,14 +9644,14 @@
           <t>rubik_knowledge_edit</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr">
-        <is>
-          <t>DELETE</t>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/knowledge/{type}/{item}</t>
+          <t>/rubik/api/databases/{id}/knowledge/experience</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -9496,11 +9679,7 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J68" s="5" t="inlineStr">
-        <is>
-          <t>contributor</t>
-        </is>
-      </c>
+      <c r="J68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="28" t="inlineStr">
@@ -9520,7 +9699,7 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/knowledge/taxonomy</t>
+          <t>/rubik/api/databases/{id}/knowledge/import</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -9558,7 +9737,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>rubik_knowledge_edit</t>
+          <t>rubik_knowledge_special</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -9568,7 +9747,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/knowledge/custom</t>
+          <t>/rubik/api/databases/knowledge/special</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -9591,12 +9770,16 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I70" s="24" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="J70" s="5" t="inlineStr"/>
+      <c r="I70" s="29" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>理想 rubik-admins only；OR 语义下被 rubik_db_view/edit POST 覆盖（已知限制）</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="28" t="inlineStr">
@@ -9606,17 +9789,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>rubik_knowledge_edit</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>rubik_knowledge_view</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/knowledge/experience</t>
+          <t>/rubik/api/databases/{id}/knowledge/types</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -9644,7 +9827,11 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J71" s="5" t="inlineStr"/>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="28" t="inlineStr">
@@ -9654,17 +9841,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>rubik_knowledge_edit</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>rubik_knowledge_view</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/knowledge/import</t>
+          <t>/rubik/api/databases/{id}/knowledge/list</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -9702,17 +9889,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>rubik_knowledge_special</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>rubik_knowledge_view</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/knowledge/special</t>
+          <t>/rubik/api/databases/{id}/knowledge/{type}</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -9735,16 +9922,12 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I73" s="29" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
-      <c r="J73" s="5" t="inlineStr">
-        <is>
-          <t>理想 rubik-admins only；OR 语义下被 rubik_db_view/edit POST 覆盖（已知限制）</t>
-        </is>
-      </c>
+      <c r="I73" s="24" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="28" t="inlineStr">
@@ -9764,7 +9947,7 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/knowledge/types</t>
+          <t>/rubik/api/databases/{id}/knowledge/{type}/{item}</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -9792,11 +9975,7 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J74" s="5" t="inlineStr">
-        <is>
-          <t>viewer</t>
-        </is>
-      </c>
+      <c r="J74" s="5" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="28" t="inlineStr">
@@ -9809,14 +9988,14 @@
           <t>rubik_knowledge_view</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/knowledge/list</t>
+          <t>/rubik/api/databases/{id}/sync</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -9844,7 +10023,11 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J75" s="5" t="inlineStr"/>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="28" t="inlineStr">
@@ -9857,14 +10040,14 @@
           <t>rubik_knowledge_view</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/knowledge/{type}</t>
+          <t>/rubik/api/databases/{id}/sync/stream</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -9905,14 +10088,14 @@
           <t>rubik_knowledge_view</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/knowledge/{type}/{item}</t>
+          <t>/rubik/api/databases/{id}/knowledge/export/stream</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -9940,7 +10123,11 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J77" s="5" t="inlineStr"/>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="28" t="inlineStr">
@@ -9950,7 +10137,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>rubik_knowledge_view</t>
+          <t>rubik_skill_manage</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
@@ -9960,7 +10147,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/sync</t>
+          <t>/rubik/api/databases/{id}/skill/custom</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -10002,17 +10189,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>rubik_knowledge_view</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>rubik_skill_manage</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/sync/stream</t>
+          <t>/rubik/api/databases/{id}/skill/{item}</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -10040,7 +10227,11 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J79" s="5" t="inlineStr"/>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>contributor</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="28" t="inlineStr">
@@ -10050,17 +10241,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>rubik_knowledge_view</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>rubik_metadata</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/knowledge/export/stream</t>
+          <t>/rubik/api/metadata/{id}/init</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -10090,7 +10281,7 @@
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>viewer</t>
+          <t>contributor (实为写)</t>
         </is>
       </c>
     </row>
@@ -10102,17 +10293,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>rubik_skill_manage</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>rubik_metadata</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/skill/custom</t>
+          <t>/rubik/api/metadata/{id}</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -10142,7 +10333,7 @@
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>contributor</t>
+          <t>viewer</t>
         </is>
       </c>
     </row>
@@ -10154,7 +10345,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>rubik_skill_manage</t>
+          <t>rubik_metadata</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
@@ -10164,7 +10355,7 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/databases/{id}/skill/{item}</t>
+          <t>/rubik/api/metadata/{id}/description</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -10206,17 +10397,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>rubik_metadata</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>rubik_query</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/metadata/{id}/init</t>
+          <t>/rubik/api/query</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -10246,7 +10437,7 @@
       </c>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>contributor (实为写)</t>
+          <t>viewer on body.database_id</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10449,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>rubik_metadata</t>
+          <t>rubik_query</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -10268,7 +10459,7 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/metadata/{id}</t>
+          <t>/rubik/api/sessions</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
@@ -10298,7 +10489,7 @@
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>viewer</t>
+          <t>X-Allowed-Ids</t>
         </is>
       </c>
     </row>
@@ -10310,17 +10501,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>rubik_metadata</t>
-        </is>
-      </c>
-      <c r="C85" s="7" t="inlineStr">
-        <is>
-          <t>PUT</t>
+          <t>rubik_query</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/metadata/{id}/description</t>
+          <t>/rubik/api/sessions</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -10343,14 +10534,14 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I85" s="24" t="inlineStr">
-        <is>
-          <t>⚡</t>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
-          <t>contributor</t>
+          <t>创建→owner</t>
         </is>
       </c>
     </row>
@@ -10365,14 +10556,14 @@
           <t>rubik_query</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/query</t>
+          <t>/rubik/api/sessions/{id}</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
@@ -10402,7 +10593,7 @@
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>viewer on body.database_id</t>
+          <t>owner</t>
         </is>
       </c>
     </row>
@@ -10417,14 +10608,14 @@
           <t>rubik_query</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/sessions</t>
+          <t>/rubik/api/sessions/replay</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -10452,11 +10643,7 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J87" s="5" t="inlineStr">
-        <is>
-          <t>X-Allowed-Ids</t>
-        </is>
-      </c>
+      <c r="J87" s="5" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="28" t="inlineStr">
@@ -10469,14 +10656,14 @@
           <t>rubik_query</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/sessions</t>
+          <t>/rubik/api/sessions/{id}/replay</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -10499,14 +10686,14 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I88" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="I88" s="24" t="inlineStr">
+        <is>
+          <t>⚡</t>
         </is>
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>创建→owner</t>
+          <t>owner</t>
         </is>
       </c>
     </row>
@@ -10521,14 +10708,14 @@
           <t>rubik_query</t>
         </is>
       </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>DELETE</t>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/sessions/{id}</t>
+          <t>/rubik/api/sessions/{id}/turns</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -10580,7 +10767,7 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/sessions/replay</t>
+          <t>/rubik/api/sessions/{id}/turns/{tid}/feedback</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -10608,7 +10795,11 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="J90" s="5" t="inlineStr"/>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="28" t="inlineStr">
@@ -10618,7 +10809,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>rubik_query</t>
+          <t>rubik_config_view</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -10628,7 +10819,7 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/sessions/{id}/replay</t>
+          <t>/rubik/api/config</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -10651,16 +10842,12 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I91" s="24" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="J91" s="5" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="28" t="inlineStr">
@@ -10670,7 +10857,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>rubik_query</t>
+          <t>rubik_config_view</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -10680,7 +10867,7 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/sessions/{id}/turns</t>
+          <t>/rubik/api/config/models</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
@@ -10703,16 +10890,12 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I92" s="24" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="J92" s="5" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="28" t="inlineStr">
@@ -10722,17 +10905,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>rubik_query</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>rubik_config_view</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/sessions/{id}/turns/{tid}/feedback</t>
+          <t>/rubik/api/config/database-providers</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -10755,16 +10938,12 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I93" s="24" t="inlineStr">
-        <is>
-          <t>⚡</t>
-        </is>
-      </c>
-      <c r="J93" s="5" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="28" t="inlineStr">
@@ -10784,7 +10963,7 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config</t>
+          <t>/rubik/api/config/language</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -10832,7 +11011,7 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/models</t>
+          <t>/rubik/api/config/app</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -10880,7 +11059,7 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/database-providers</t>
+          <t>/rubik/api/config/paths/logs</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -10928,7 +11107,7 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/language</t>
+          <t>/rubik/api/config/llm-providers</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -10966,17 +11145,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>rubik_config_view</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>rubik_config_manage</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/app</t>
+          <t>/rubik/api/config/models/{name}</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
@@ -10999,12 +11178,16 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I98" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J98" s="5" t="inlineStr"/>
+      <c r="I98" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>rubik-admins 专属</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="28" t="inlineStr">
@@ -11014,17 +11197,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>rubik_config_view</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>rubik_config_manage</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/paths/logs</t>
+          <t>/rubik/api/config/database-providers/{p}</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -11047,9 +11230,9 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I99" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="J99" s="5" t="inlineStr"/>
@@ -11062,17 +11245,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>rubik_config_view</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>rubik_config_manage</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/llm-providers</t>
+          <t>/rubik/api/config/language</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -11095,9 +11278,9 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I100" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="J100" s="5" t="inlineStr"/>
@@ -11120,7 +11303,7 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/models/{name}</t>
+          <t>/rubik/api/config/languages</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -11148,11 +11331,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="J101" s="5" t="inlineStr">
-        <is>
-          <t>rubik-admins 专属</t>
-        </is>
-      </c>
+      <c r="J101" s="5" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="28" t="inlineStr">
@@ -11172,7 +11351,7 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/database-providers/{p}</t>
+          <t>/rubik/api/config/app/{key}</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -11213,14 +11392,14 @@
           <t>rubik_config_manage</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
-        <is>
-          <t>PUT</t>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/language</t>
+          <t>/rubik/api/config/reload</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -11261,14 +11440,14 @@
           <t>rubik_config_manage</t>
         </is>
       </c>
-      <c r="C104" s="7" t="inlineStr">
-        <is>
-          <t>PUT</t>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/languages</t>
+          <t>/rubik/api/config/setup</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -11309,14 +11488,14 @@
           <t>rubik_config_manage</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
-        <is>
-          <t>PUT</t>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/app/{key}</t>
+          <t>/rubik/api/config/open-path</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -11364,7 +11543,7 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/reload</t>
+          <t>/rubik/api/config/llm-providers</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -11405,14 +11584,14 @@
           <t>rubik_config_manage</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/setup</t>
+          <t>/rubik/api/config/llm-providers/{name}</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -11453,14 +11632,14 @@
           <t>rubik_config_manage</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/open-path</t>
+          <t>/rubik/api/config/llm-providers/{name}</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -11498,17 +11677,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>rubik_config_manage</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>rubik_dashboard_view</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/llm-providers</t>
+          <t>/rubik/api/dashboards</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -11531,9 +11710,9 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I109" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr"/>
@@ -11546,17 +11725,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>rubik_config_manage</t>
-        </is>
-      </c>
-      <c r="C110" s="7" t="inlineStr">
-        <is>
-          <t>PUT</t>
+          <t>rubik_dashboard_view</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/llm-providers/{name}</t>
+          <t>/rubik/api/dashboards/{id}</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -11579,9 +11758,9 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I110" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr"/>
@@ -11594,17 +11773,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>rubik_config_manage</t>
-        </is>
-      </c>
-      <c r="C111" s="8" t="inlineStr">
-        <is>
-          <t>DELETE</t>
+          <t>rubik_dashboard_edit</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/config/llm-providers/{name}</t>
+          <t>/rubik/api/dashboards</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -11627,9 +11806,9 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="I111" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr"/>
@@ -11642,17 +11821,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>rubik_dashboard_view</t>
-        </is>
-      </c>
-      <c r="C112" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>rubik_dashboard_edit</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/dashboards</t>
+          <t>/rubik/api/dashboards/{id}</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -11690,12 +11869,12 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>rubik_dashboard_view</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>rubik_dashboard_edit</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
@@ -11738,17 +11917,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>rubik_dashboard_edit</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>rubik_db_refresh</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/dashboards</t>
+          <t>/rubik/api/refresh/{id}/status</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -11786,17 +11965,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>rubik_dashboard_edit</t>
-        </is>
-      </c>
-      <c r="C115" s="7" t="inlineStr">
-        <is>
-          <t>PUT</t>
+          <t>rubik_db_refresh</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/dashboards/{id}</t>
+          <t>/rubik/api/refresh/{id}/execute/stream</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -11827,24 +12006,24 @@
       <c r="J115" s="5" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="28" t="inlineStr">
-        <is>
-          <t>Rubik</t>
+      <c r="A116" s="30" t="inlineStr">
+        <is>
+          <t>Memory</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>rubik_dashboard_edit</t>
-        </is>
-      </c>
-      <c r="C116" s="8" t="inlineStr">
-        <is>
-          <t>DELETE</t>
+          <t>memory_health</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/dashboards/{id}</t>
+          <t>/memory/api/v1/health</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
@@ -11857,14 +12036,14 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="G116" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H116" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr">
@@ -11875,24 +12054,24 @@
       <c r="J116" s="5" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="28" t="inlineStr">
-        <is>
-          <t>Rubik</t>
+      <c r="A117" s="30" t="inlineStr">
+        <is>
+          <t>Memory</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>rubik_db_refresh</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>memory_user_data</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/refresh/{id}/status</t>
+          <t>/memory/api/v1/memory/add</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -11905,14 +12084,14 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="G117" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H117" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
@@ -11923,14 +12102,14 @@
       <c r="J117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="28" t="inlineStr">
-        <is>
-          <t>Rubik</t>
+      <c r="A118" s="30" t="inlineStr">
+        <is>
+          <t>Memory</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>rubik_db_refresh</t>
+          <t>memory_user_data</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
@@ -11940,7 +12119,7 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>/rubik/api/refresh/{id}/execute/stream</t>
+          <t>/memory/api/v1/memory/query</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -11953,14 +12132,14 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="G118" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H118" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I118" s="4" t="inlineStr">
@@ -11978,17 +12157,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>memory_health</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>memory_user_data</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/health</t>
+          <t>/memory/api/v1/memory/update</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -12036,7 +12215,7 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/memory/add</t>
+          <t>/memory/api/v1/memory/delete</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
@@ -12074,17 +12253,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>memory_user_data</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>memory_user_templates_read</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/memory/query</t>
+          <t>/memory/api/v1/templates</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -12112,7 +12291,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J121" s="5" t="inlineStr"/>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>all-users 只读（含子路径 GET）</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="30" t="inlineStr">
@@ -12122,17 +12305,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>memory_user_data</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>memory_user_templates_read</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/memory/update</t>
+          <t>/memory/api/v1/templates/{id}</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -12170,17 +12353,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>memory_user_data</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
+          <t>memory_user_templates_read</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>GET</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/memory/delete</t>
+          <t>/memory/api/v1/templates/{id}/filters</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -12218,17 +12401,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>memory_user_templates_read</t>
-        </is>
-      </c>
-      <c r="C124" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>memory_tenant_admin</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/templates</t>
+          <t>/memory/api/v1/tenants/{id}</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
@@ -12251,14 +12434,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I124" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="I124" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>all-users 只读（含子路径 GET）</t>
+          <t>trailing-/ 匹配</t>
         </is>
       </c>
     </row>
@@ -12270,17 +12453,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>memory_user_templates_read</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>memory_tenant_admin</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/templates/{id}</t>
+          <t>/memory/api/v1/tenants/{id}/instances</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -12303,9 +12486,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I125" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="I125" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr"/>
@@ -12318,17 +12501,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>memory_user_templates_read</t>
-        </is>
-      </c>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>GET</t>
+          <t>memory_tenant_admin</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="inlineStr">
+        <is>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/templates/{id}/filters</t>
+          <t>/memory/api/v1/tenants/{id}/instances/{name}</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -12351,9 +12534,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I126" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="I126" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr"/>
@@ -12376,7 +12559,7 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/tenants/{id}</t>
+          <t>/memory/api/v1/tenants/{id}/instances/{n}/users/{u}/memories</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -12406,7 +12589,7 @@
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>trailing-/ 匹配</t>
+          <t>OR 语义：path 级允许，业务规程再限制入口</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12611,7 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/tenants/{id}/instances</t>
+          <t>/memory/api/v1/templates</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
@@ -12469,14 +12652,14 @@
           <t>memory_tenant_admin</t>
         </is>
       </c>
-      <c r="C129" s="8" t="inlineStr">
-        <is>
-          <t>DELETE</t>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>PUT</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/tenants/{id}/instances/{name}</t>
+          <t>/memory/api/v1/templates/{id}</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -12524,7 +12707,7 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/tenants/{id}/instances/{n}/users/{u}/memories</t>
+          <t>/memory/api/v1/templates/{id}</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
@@ -12552,11 +12735,7 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="J130" s="5" t="inlineStr">
-        <is>
-          <t>OR 语义：path 级允许，业务规程再限制入口</t>
-        </is>
-      </c>
+      <c r="J130" s="5" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="30" t="inlineStr">
@@ -12576,7 +12755,7 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/templates</t>
+          <t>/memory/api/v1/templates/{id}/filters</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -12617,14 +12796,14 @@
           <t>memory_tenant_admin</t>
         </is>
       </c>
-      <c r="C132" s="7" t="inlineStr">
-        <is>
-          <t>PUT</t>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/templates/{id}</t>
+          <t>/memory/api/v1/templates/{id}/llm-extraction</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
@@ -12665,14 +12844,14 @@
           <t>memory_tenant_admin</t>
         </is>
       </c>
-      <c r="C133" s="8" t="inlineStr">
-        <is>
-          <t>DELETE</t>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>POST</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/templates/{id}</t>
+          <t>/memory/api/v1/templates/batch/llm-extraction</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -12710,7 +12889,7 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>memory_tenant_admin</t>
+          <t>memory_admin_full</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
@@ -12720,7 +12899,7 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/templates/{id}/filters</t>
+          <t>/memory/api/v1/tenants</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
@@ -12738,9 +12917,9 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="H134" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="H134" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="I134" s="8" t="inlineStr">
@@ -12748,7 +12927,11 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="J134" s="5" t="inlineStr"/>
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t>创建 tenant — admins 专属（trailing-/ 排除 memory_tenant_admin）</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="30" t="inlineStr">
@@ -12758,7 +12941,7 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>memory_tenant_admin</t>
+          <t>memory_admin_full</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -12768,7 +12951,7 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>/memory/api/v1/templates/{id}/llm-extraction</t>
+          <t>/memory/api/v1/system/recovery</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -12786,9 +12969,9 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="H135" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="H135" s="8" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="I135" s="8" t="inlineStr">
@@ -12796,162 +12979,14 @@
           <t>✗</t>
         </is>
       </c>
-      <c r="J135" s="5" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="30" t="inlineStr">
-        <is>
-          <t>Memory</t>
-        </is>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>memory_tenant_admin</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>/memory/api/v1/templates/batch/llm-extraction</t>
-        </is>
-      </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F136" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="G136" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I136" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="J136" s="5" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="30" t="inlineStr">
-        <is>
-          <t>Memory</t>
-        </is>
-      </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>memory_admin_full</t>
-        </is>
-      </c>
-      <c r="C137" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D137" s="5" t="inlineStr">
-        <is>
-          <t>/memory/api/v1/tenants</t>
-        </is>
-      </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F137" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="G137" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H137" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="I137" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="J137" s="5" t="inlineStr">
-        <is>
-          <t>创建 tenant — admins 专属（trailing-/ 排除 memory_tenant_admin）</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="30" t="inlineStr">
-        <is>
-          <t>Memory</t>
-        </is>
-      </c>
-      <c r="B138" s="5" t="inlineStr">
-        <is>
-          <t>memory_admin_full</t>
-        </is>
-      </c>
-      <c r="C138" s="6" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="D138" s="5" t="inlineStr">
-        <is>
-          <t>/memory/api/v1/system/recovery</t>
-        </is>
-      </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F138" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="G138" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H138" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="I138" s="8" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="J138" s="5" t="inlineStr">
+      <c r="J135" s="5" t="inlineStr">
         <is>
           <t>系统恢复 — admins 专属</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J138"/>
+  <autoFilter ref="A1:J135"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>